--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>FNV</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1809700</v>
+        <v>1649600</v>
       </c>
       <c r="E8" s="3">
-        <v>1788200</v>
+        <v>1780400</v>
       </c>
       <c r="F8" s="3">
-        <v>1403300</v>
+        <v>1759200</v>
       </c>
       <c r="G8" s="3">
-        <v>1161100</v>
+        <v>1380500</v>
       </c>
       <c r="H8" s="3">
-        <v>898500</v>
+        <v>1142200</v>
       </c>
       <c r="I8" s="3">
-        <v>928500</v>
+        <v>883900</v>
       </c>
       <c r="J8" s="3">
+        <v>913400</v>
+      </c>
+      <c r="K8" s="3">
         <v>839300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>613400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>563500</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>637000</v>
+        <v>612200</v>
       </c>
       <c r="E9" s="3">
-        <v>657400</v>
+        <v>626700</v>
       </c>
       <c r="F9" s="3">
-        <v>549900</v>
+        <v>646700</v>
       </c>
       <c r="G9" s="3">
-        <v>561200</v>
+        <v>541000</v>
       </c>
       <c r="H9" s="3">
-        <v>503300</v>
+        <v>552100</v>
       </c>
       <c r="I9" s="3">
-        <v>570800</v>
+        <v>495100</v>
       </c>
       <c r="J9" s="3">
+        <v>561600</v>
+      </c>
+      <c r="K9" s="3">
         <v>522100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>128700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>92900</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1172800</v>
+        <v>1037400</v>
       </c>
       <c r="E10" s="3">
-        <v>1130800</v>
+        <v>1153700</v>
       </c>
       <c r="F10" s="3">
-        <v>853400</v>
+        <v>1112500</v>
       </c>
       <c r="G10" s="3">
-        <v>599900</v>
+        <v>839500</v>
       </c>
       <c r="H10" s="3">
-        <v>395200</v>
+        <v>590100</v>
       </c>
       <c r="I10" s="3">
-        <v>357600</v>
+        <v>388800</v>
       </c>
       <c r="J10" s="3">
+        <v>351800</v>
+      </c>
+      <c r="K10" s="3">
         <v>317200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>484600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>470700</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -842,21 +855,24 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
-        <v>5000</v>
+      <c r="I12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J12" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K12" s="3">
         <v>4700</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2800</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,75 +903,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1587700</v>
       </c>
       <c r="E14" s="3">
-        <v>-93500</v>
+        <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>360500</v>
+        <v>-92000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>354700</v>
       </c>
       <c r="H14" s="3">
-        <v>104500</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>6200</v>
+        <v>102800</v>
       </c>
       <c r="J14" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K14" s="3">
         <v>73500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>89700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>40100</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>299100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>207800</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>680900</v>
+        <v>2228700</v>
       </c>
       <c r="E17" s="3">
-        <v>604300</v>
+        <v>669800</v>
       </c>
       <c r="F17" s="3">
-        <v>940400</v>
+        <v>594500</v>
       </c>
       <c r="G17" s="3">
-        <v>596800</v>
+        <v>925200</v>
       </c>
       <c r="H17" s="3">
-        <v>638800</v>
+        <v>587200</v>
       </c>
       <c r="I17" s="3">
-        <v>610900</v>
+        <v>628400</v>
       </c>
       <c r="J17" s="3">
+        <v>601000</v>
+      </c>
+      <c r="K17" s="3">
         <v>625600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>542200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>364400</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1128900</v>
+        <v>-579200</v>
       </c>
       <c r="E18" s="3">
-        <v>1183900</v>
+        <v>1110600</v>
       </c>
       <c r="F18" s="3">
-        <v>462900</v>
+        <v>1164700</v>
       </c>
       <c r="G18" s="3">
-        <v>564200</v>
+        <v>455400</v>
       </c>
       <c r="H18" s="3">
-        <v>259700</v>
+        <v>555100</v>
       </c>
       <c r="I18" s="3">
-        <v>317600</v>
+        <v>255500</v>
       </c>
       <c r="J18" s="3">
+        <v>312500</v>
+      </c>
+      <c r="K18" s="3">
         <v>213800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>71200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>199100</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,91 +1079,98 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19300</v>
+        <v>87100</v>
       </c>
       <c r="E20" s="3">
-        <v>-2100</v>
+        <v>18900</v>
       </c>
       <c r="F20" s="3">
-        <v>6100</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>5800</v>
+        <v>6000</v>
       </c>
       <c r="H20" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>7000</v>
-      </c>
       <c r="J20" s="3">
+        <v>6900</v>
+      </c>
+      <c r="K20" s="3">
         <v>17200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>900</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1539600</v>
+        <v>-124200</v>
       </c>
       <c r="E21" s="3">
-        <v>1591600</v>
+        <v>1515000</v>
       </c>
       <c r="F21" s="3">
-        <v>798500</v>
+        <v>1566200</v>
       </c>
       <c r="G21" s="3">
-        <v>930000</v>
+        <v>785900</v>
       </c>
       <c r="H21" s="3">
-        <v>598900</v>
+        <v>915300</v>
       </c>
       <c r="I21" s="3">
-        <v>698000</v>
+        <v>589500</v>
       </c>
       <c r="J21" s="3">
+        <v>687100</v>
+      </c>
+      <c r="K21" s="3">
         <v>605500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>365600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>408500</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1900</v>
       </c>
       <c r="F22" s="3">
         <v>1900</v>
       </c>
       <c r="G22" s="3">
-        <v>11700</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
+        <v>1900</v>
+      </c>
+      <c r="H22" s="3">
+        <v>11500</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -1145,75 +1184,84 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1146800</v>
+        <v>-492800</v>
       </c>
       <c r="E23" s="3">
-        <v>1179900</v>
+        <v>1128200</v>
       </c>
       <c r="F23" s="3">
-        <v>467000</v>
+        <v>1160800</v>
       </c>
       <c r="G23" s="3">
-        <v>558300</v>
+        <v>459400</v>
       </c>
       <c r="H23" s="3">
-        <v>260100</v>
+        <v>549300</v>
       </c>
       <c r="I23" s="3">
-        <v>324600</v>
+        <v>255900</v>
       </c>
       <c r="J23" s="3">
+        <v>319400</v>
+      </c>
+      <c r="K23" s="3">
         <v>230900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>67100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>200000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>183100</v>
+        <v>138300</v>
       </c>
       <c r="E24" s="3">
-        <v>170700</v>
+        <v>180100</v>
       </c>
       <c r="F24" s="3">
-        <v>18300</v>
+        <v>167900</v>
       </c>
       <c r="G24" s="3">
-        <v>85000</v>
+        <v>18000</v>
       </c>
       <c r="H24" s="3">
-        <v>66200</v>
+        <v>83600</v>
       </c>
       <c r="I24" s="3">
-        <v>47000</v>
+        <v>65100</v>
       </c>
       <c r="J24" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K24" s="3">
         <v>62900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>64100</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>963700</v>
+        <v>-631100</v>
       </c>
       <c r="E26" s="3">
-        <v>1009200</v>
+        <v>948100</v>
       </c>
       <c r="F26" s="3">
-        <v>448700</v>
+        <v>992800</v>
       </c>
       <c r="G26" s="3">
-        <v>473300</v>
+        <v>441400</v>
       </c>
       <c r="H26" s="3">
-        <v>193900</v>
+        <v>465600</v>
       </c>
       <c r="I26" s="3">
-        <v>277600</v>
+        <v>190800</v>
       </c>
       <c r="J26" s="3">
+        <v>273100</v>
+      </c>
+      <c r="K26" s="3">
         <v>168100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>135900</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>963700</v>
+        <v>-631100</v>
       </c>
       <c r="E27" s="3">
-        <v>1009200</v>
+        <v>948100</v>
       </c>
       <c r="F27" s="3">
-        <v>448700</v>
+        <v>992800</v>
       </c>
       <c r="G27" s="3">
-        <v>473300</v>
+        <v>441400</v>
       </c>
       <c r="H27" s="3">
-        <v>193900</v>
+        <v>465600</v>
       </c>
       <c r="I27" s="3">
-        <v>277600</v>
+        <v>190800</v>
       </c>
       <c r="J27" s="3">
+        <v>273100</v>
+      </c>
+      <c r="K27" s="3">
         <v>168100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>135900</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1361,14 +1421,14 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>-2800</v>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>-2700</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-9600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1376,9 +1436,12 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19300</v>
+        <v>-87100</v>
       </c>
       <c r="E32" s="3">
-        <v>2100</v>
+        <v>-18900</v>
       </c>
       <c r="F32" s="3">
-        <v>-6100</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>-5800</v>
+        <v>-6000</v>
       </c>
       <c r="H32" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>-7000</v>
-      </c>
       <c r="J32" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-17200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-900</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>963700</v>
+        <v>-631100</v>
       </c>
       <c r="E33" s="3">
-        <v>1009200</v>
+        <v>948100</v>
       </c>
       <c r="F33" s="3">
-        <v>448700</v>
+        <v>992800</v>
       </c>
       <c r="G33" s="3">
-        <v>473300</v>
+        <v>441400</v>
       </c>
       <c r="H33" s="3">
-        <v>191200</v>
+        <v>465600</v>
       </c>
       <c r="I33" s="3">
-        <v>267800</v>
+        <v>188100</v>
       </c>
       <c r="J33" s="3">
+        <v>263500</v>
+      </c>
+      <c r="K33" s="3">
         <v>168100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>135900</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>963700</v>
+        <v>-631100</v>
       </c>
       <c r="E35" s="3">
-        <v>1009200</v>
+        <v>948100</v>
       </c>
       <c r="F35" s="3">
-        <v>448700</v>
+        <v>992800</v>
       </c>
       <c r="G35" s="3">
-        <v>473300</v>
+        <v>441400</v>
       </c>
       <c r="H35" s="3">
-        <v>191200</v>
+        <v>465600</v>
       </c>
       <c r="I35" s="3">
-        <v>267800</v>
+        <v>188100</v>
       </c>
       <c r="J35" s="3">
+        <v>263500</v>
+      </c>
+      <c r="K35" s="3">
         <v>168100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>135900</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1645800</v>
+        <v>1924100</v>
       </c>
       <c r="E41" s="3">
-        <v>741800</v>
+        <v>1619100</v>
       </c>
       <c r="F41" s="3">
-        <v>734800</v>
+        <v>729800</v>
       </c>
       <c r="G41" s="3">
-        <v>181700</v>
+        <v>722900</v>
       </c>
       <c r="H41" s="3">
-        <v>95900</v>
+        <v>178800</v>
       </c>
       <c r="I41" s="3">
-        <v>703000</v>
+        <v>94300</v>
       </c>
       <c r="J41" s="3">
+        <v>691600</v>
+      </c>
+      <c r="K41" s="3">
         <v>348000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>206300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>754700</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1703,47 +1792,53 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>26000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>186700</v>
+        <v>150200</v>
       </c>
       <c r="E43" s="3">
-        <v>219400</v>
+        <v>183600</v>
       </c>
       <c r="F43" s="3">
-        <v>128500</v>
+        <v>215800</v>
       </c>
       <c r="G43" s="3">
-        <v>134500</v>
+        <v>126400</v>
       </c>
       <c r="H43" s="3">
-        <v>103900</v>
+        <v>132300</v>
       </c>
       <c r="I43" s="3">
-        <v>90600</v>
+        <v>102200</v>
       </c>
       <c r="J43" s="3">
+        <v>89200</v>
+      </c>
+      <c r="K43" s="3">
         <v>97800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>90000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>91800</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1759,156 +1854,171 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
-        <v>0</v>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I44" s="3">
-        <v>9800</v>
+        <v>0</v>
       </c>
       <c r="J44" s="3">
+        <v>9600</v>
+      </c>
+      <c r="K44" s="3">
         <v>3700</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>70000</v>
+        <v>111500</v>
       </c>
       <c r="E45" s="3">
-        <v>72400</v>
+        <v>68900</v>
       </c>
       <c r="F45" s="3">
-        <v>49700</v>
+        <v>71200</v>
       </c>
       <c r="G45" s="3">
-        <v>67100</v>
+        <v>48900</v>
       </c>
       <c r="H45" s="3">
-        <v>45800</v>
+        <v>66000</v>
       </c>
       <c r="I45" s="3">
-        <v>44400</v>
+        <v>45100</v>
       </c>
       <c r="J45" s="3">
+        <v>43700</v>
+      </c>
+      <c r="K45" s="3">
         <v>47300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>57500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>43700</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1902500</v>
+        <v>2185800</v>
       </c>
       <c r="E46" s="3">
-        <v>1033600</v>
+        <v>1871600</v>
       </c>
       <c r="F46" s="3">
-        <v>912900</v>
+        <v>1016800</v>
       </c>
       <c r="G46" s="3">
-        <v>383400</v>
+        <v>898100</v>
       </c>
       <c r="H46" s="3">
-        <v>245500</v>
+        <v>377100</v>
       </c>
       <c r="I46" s="3">
-        <v>847900</v>
+        <v>241500</v>
       </c>
       <c r="J46" s="3">
+        <v>834100</v>
+      </c>
+      <c r="K46" s="3">
         <v>496800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>379800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>890300</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>308900</v>
+        <v>367000</v>
       </c>
       <c r="E47" s="3">
-        <v>323400</v>
+        <v>303900</v>
       </c>
       <c r="F47" s="3">
-        <v>320100</v>
+        <v>318100</v>
       </c>
       <c r="G47" s="3">
-        <v>247900</v>
+        <v>314900</v>
       </c>
       <c r="H47" s="3">
-        <v>232500</v>
+        <v>243800</v>
       </c>
       <c r="I47" s="3">
-        <v>278300</v>
+        <v>228700</v>
       </c>
       <c r="J47" s="3">
+        <v>273800</v>
+      </c>
+      <c r="K47" s="3">
         <v>201500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>130900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>84700</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6787000</v>
+        <v>5458400</v>
       </c>
       <c r="E48" s="3">
-        <v>7092600</v>
+        <v>6677000</v>
       </c>
       <c r="F48" s="3">
-        <v>6381600</v>
+        <v>6977600</v>
       </c>
       <c r="G48" s="3">
-        <v>6616200</v>
+        <v>6278200</v>
       </c>
       <c r="H48" s="3">
-        <v>6280900</v>
+        <v>6508900</v>
       </c>
       <c r="I48" s="3">
-        <v>5436700</v>
+        <v>6179100</v>
       </c>
       <c r="J48" s="3">
+        <v>5348500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5066000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4527800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3358900</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1939,9 +2049,12 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,42 +2121,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>116800</v>
+        <v>100000</v>
       </c>
       <c r="E52" s="3">
-        <v>92200</v>
+        <v>114900</v>
       </c>
       <c r="F52" s="3">
-        <v>78400</v>
+        <v>90700</v>
       </c>
       <c r="G52" s="3">
-        <v>16100</v>
+        <v>77100</v>
       </c>
       <c r="H52" s="3">
-        <v>24800</v>
+        <v>15800</v>
       </c>
       <c r="I52" s="3">
-        <v>23700</v>
+        <v>24400</v>
       </c>
       <c r="J52" s="3">
+        <v>23300</v>
+      </c>
+      <c r="K52" s="3">
         <v>42500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>82300</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>9115200</v>
+        <v>8111200</v>
       </c>
       <c r="E54" s="3">
-        <v>8541700</v>
+        <v>8967400</v>
       </c>
       <c r="F54" s="3">
-        <v>7693000</v>
+        <v>8403200</v>
       </c>
       <c r="G54" s="3">
-        <v>7263500</v>
+        <v>7568300</v>
       </c>
       <c r="H54" s="3">
-        <v>6783700</v>
+        <v>7145700</v>
       </c>
       <c r="I54" s="3">
-        <v>6586400</v>
+        <v>6673700</v>
       </c>
       <c r="J54" s="3">
+        <v>6479700</v>
+      </c>
+      <c r="K54" s="3">
         <v>5806800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5080500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4416100</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,41 +2264,45 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9600</v>
+        <v>7400</v>
       </c>
       <c r="E57" s="3">
-        <v>11700</v>
+        <v>9500</v>
       </c>
       <c r="F57" s="3">
-        <v>4800</v>
+        <v>11500</v>
       </c>
       <c r="G57" s="3">
-        <v>9400</v>
+        <v>4700</v>
       </c>
       <c r="H57" s="3">
-        <v>10000</v>
+        <v>9200</v>
       </c>
       <c r="I57" s="3">
-        <v>8500</v>
+        <v>9900</v>
       </c>
       <c r="J57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K57" s="3">
         <v>13200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7900</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2200,75 +2333,84 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>59400</v>
+        <v>45600</v>
       </c>
       <c r="E59" s="3">
-        <v>47700</v>
+        <v>58500</v>
       </c>
       <c r="F59" s="3">
-        <v>68400</v>
+        <v>47000</v>
       </c>
       <c r="G59" s="3">
-        <v>64100</v>
+        <v>67300</v>
       </c>
       <c r="H59" s="3">
-        <v>24300</v>
+        <v>63100</v>
       </c>
       <c r="I59" s="3">
-        <v>22600</v>
+        <v>24000</v>
       </c>
       <c r="J59" s="3">
+        <v>22200</v>
+      </c>
+      <c r="K59" s="3">
         <v>38500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>19000</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>69100</v>
+        <v>53000</v>
       </c>
       <c r="E60" s="3">
-        <v>59400</v>
+        <v>67900</v>
       </c>
       <c r="F60" s="3">
-        <v>73200</v>
+        <v>58500</v>
       </c>
       <c r="G60" s="3">
-        <v>73500</v>
+        <v>72000</v>
       </c>
       <c r="H60" s="3">
-        <v>34400</v>
+        <v>72300</v>
       </c>
       <c r="I60" s="3">
-        <v>31100</v>
+        <v>33800</v>
       </c>
       <c r="J60" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K60" s="3">
         <v>51700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26900</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2282,59 +2424,65 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>113600</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>285600</v>
+        <v>111800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>280900</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>632300</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>218700</v>
+        <v>251400</v>
       </c>
       <c r="E62" s="3">
-        <v>194600</v>
+        <v>215200</v>
       </c>
       <c r="F62" s="3">
-        <v>131900</v>
+        <v>191500</v>
       </c>
       <c r="G62" s="3">
-        <v>113300</v>
+        <v>129800</v>
       </c>
       <c r="H62" s="3">
-        <v>92600</v>
+        <v>111500</v>
       </c>
       <c r="I62" s="3">
-        <v>82900</v>
+        <v>91100</v>
       </c>
       <c r="J62" s="3">
+        <v>81600</v>
+      </c>
+      <c r="K62" s="3">
         <v>51600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>51300</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>287800</v>
+        <v>304500</v>
       </c>
       <c r="E66" s="3">
-        <v>254100</v>
+        <v>283100</v>
       </c>
       <c r="F66" s="3">
-        <v>205100</v>
+        <v>249900</v>
       </c>
       <c r="G66" s="3">
-        <v>300400</v>
+        <v>201800</v>
       </c>
       <c r="H66" s="3">
-        <v>412500</v>
+        <v>295500</v>
       </c>
       <c r="I66" s="3">
-        <v>114000</v>
+        <v>405800</v>
       </c>
       <c r="J66" s="3">
+        <v>112200</v>
+      </c>
+      <c r="K66" s="3">
         <v>103300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>707000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>78200</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2578,9 +2745,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>1293500</v>
+        <v>287300</v>
       </c>
       <c r="E72" s="3">
-        <v>667000</v>
+        <v>1272500</v>
       </c>
       <c r="F72" s="3">
-        <v>-47300</v>
+        <v>656200</v>
       </c>
       <c r="G72" s="3">
-        <v>-226100</v>
+        <v>-46600</v>
       </c>
       <c r="H72" s="3">
-        <v>-442500</v>
+        <v>-222500</v>
       </c>
       <c r="I72" s="3">
-        <v>-426400</v>
+        <v>-435300</v>
       </c>
       <c r="J72" s="3">
+        <v>-419500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-463300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-417900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-252000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>8827400</v>
+        <v>7806700</v>
       </c>
       <c r="E76" s="3">
-        <v>8287700</v>
+        <v>8684300</v>
       </c>
       <c r="F76" s="3">
-        <v>7487900</v>
+        <v>8153300</v>
       </c>
       <c r="G76" s="3">
-        <v>6963100</v>
+        <v>7366600</v>
       </c>
       <c r="H76" s="3">
-        <v>6371200</v>
+        <v>6850200</v>
       </c>
       <c r="I76" s="3">
-        <v>6472400</v>
+        <v>6267900</v>
       </c>
       <c r="J76" s="3">
+        <v>6367500</v>
+      </c>
+      <c r="K76" s="3">
         <v>5703500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4373500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4337900</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>963700</v>
+        <v>-631100</v>
       </c>
       <c r="E81" s="3">
-        <v>1009200</v>
+        <v>948100</v>
       </c>
       <c r="F81" s="3">
-        <v>448700</v>
+        <v>992800</v>
       </c>
       <c r="G81" s="3">
-        <v>473300</v>
+        <v>441400</v>
       </c>
       <c r="H81" s="3">
-        <v>191200</v>
+        <v>465600</v>
       </c>
       <c r="I81" s="3">
-        <v>267800</v>
+        <v>188100</v>
       </c>
       <c r="J81" s="3">
+        <v>263500</v>
+      </c>
+      <c r="K81" s="3">
         <v>168100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>135900</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>393700</v>
+        <v>369600</v>
       </c>
       <c r="E83" s="3">
-        <v>412100</v>
+        <v>387300</v>
       </c>
       <c r="F83" s="3">
-        <v>331500</v>
+        <v>405400</v>
       </c>
       <c r="G83" s="3">
-        <v>362000</v>
+        <v>326100</v>
       </c>
       <c r="H83" s="3">
-        <v>340700</v>
+        <v>356200</v>
       </c>
       <c r="I83" s="3">
-        <v>375500</v>
+        <v>335200</v>
       </c>
       <c r="J83" s="3">
+        <v>369400</v>
+      </c>
+      <c r="K83" s="3">
         <v>376600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>299100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>207800</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1374800</v>
+        <v>1341300</v>
       </c>
       <c r="E89" s="3">
-        <v>1314200</v>
+        <v>1352500</v>
       </c>
       <c r="F89" s="3">
-        <v>1105800</v>
+        <v>1292800</v>
       </c>
       <c r="G89" s="3">
-        <v>849600</v>
+        <v>1087800</v>
       </c>
       <c r="H89" s="3">
-        <v>653100</v>
+        <v>835900</v>
       </c>
       <c r="I89" s="3">
-        <v>672100</v>
+        <v>642500</v>
       </c>
       <c r="J89" s="3">
+        <v>661200</v>
+      </c>
+      <c r="K89" s="3">
         <v>647900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>434600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>340100</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-194600</v>
+        <v>-705800</v>
       </c>
       <c r="E91" s="3">
-        <v>-1046100</v>
+        <v>-191500</v>
       </c>
       <c r="F91" s="3">
-        <v>-430000</v>
+        <v>-1029100</v>
       </c>
       <c r="G91" s="3">
-        <v>-612400</v>
+        <v>-423000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1361200</v>
+        <v>-602400</v>
       </c>
       <c r="I91" s="3">
-        <v>-689400</v>
+        <v>-1339100</v>
       </c>
       <c r="J91" s="3">
+        <v>-678200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1027600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1410900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1135800</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-200100</v>
+        <v>-732200</v>
       </c>
       <c r="E94" s="3">
-        <v>-1052300</v>
+        <v>-196900</v>
       </c>
       <c r="F94" s="3">
-        <v>-425000</v>
+        <v>-1035200</v>
       </c>
       <c r="G94" s="3">
-        <v>-599900</v>
+        <v>-418100</v>
       </c>
       <c r="H94" s="3">
-        <v>-1360000</v>
+        <v>-590100</v>
       </c>
       <c r="I94" s="3">
-        <v>-689000</v>
+        <v>-1337900</v>
       </c>
       <c r="J94" s="3">
+        <v>-677800</v>
+      </c>
+      <c r="K94" s="3">
         <v>-948800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1529400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1039300</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-271800</v>
+        <v>-315300</v>
       </c>
       <c r="E96" s="3">
-        <v>-247000</v>
+        <v>-267400</v>
       </c>
       <c r="F96" s="3">
-        <v>-213100</v>
+        <v>-243000</v>
       </c>
       <c r="G96" s="3">
-        <v>-190100</v>
+        <v>-209600</v>
       </c>
       <c r="H96" s="3">
-        <v>-187200</v>
+        <v>-187000</v>
       </c>
       <c r="I96" s="3">
-        <v>-173000</v>
+        <v>-184200</v>
       </c>
       <c r="J96" s="3">
+        <v>-170200</v>
+      </c>
+      <c r="K96" s="3">
         <v>-162400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-130100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-115500</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-260000</v>
+        <v>-311400</v>
       </c>
       <c r="E100" s="3">
-        <v>-247900</v>
+        <v>-255800</v>
       </c>
       <c r="F100" s="3">
-        <v>-126300</v>
+        <v>-243800</v>
       </c>
       <c r="G100" s="3">
-        <v>-164800</v>
+        <v>-124200</v>
       </c>
       <c r="H100" s="3">
-        <v>106700</v>
+        <v>-162100</v>
       </c>
       <c r="I100" s="3">
-        <v>329700</v>
+        <v>105000</v>
       </c>
       <c r="J100" s="3">
+        <v>324400</v>
+      </c>
+      <c r="K100" s="3">
         <v>442500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>517300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>502800</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-10700</v>
+        <v>7300</v>
       </c>
       <c r="E101" s="3">
-        <v>-7000</v>
+        <v>-10600</v>
       </c>
       <c r="F101" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>800</v>
       </c>
-      <c r="H101" s="3">
-        <v>-7000</v>
-      </c>
       <c r="I101" s="3">
-        <v>42200</v>
+        <v>-6900</v>
       </c>
       <c r="J101" s="3">
+        <v>41500</v>
+      </c>
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-35400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-29700</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>904000</v>
+        <v>305000</v>
       </c>
       <c r="E102" s="3">
-        <v>7000</v>
+        <v>889300</v>
       </c>
       <c r="F102" s="3">
-        <v>553100</v>
+        <v>6900</v>
       </c>
       <c r="G102" s="3">
-        <v>85800</v>
+        <v>544100</v>
       </c>
       <c r="H102" s="3">
-        <v>-607100</v>
+        <v>84400</v>
       </c>
       <c r="I102" s="3">
-        <v>355000</v>
+        <v>-597300</v>
       </c>
       <c r="J102" s="3">
+        <v>349300</v>
+      </c>
+      <c r="K102" s="3">
         <v>142800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-613000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-226100</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1649600</v>
+        <v>1672700</v>
       </c>
       <c r="E8" s="3">
-        <v>1780400</v>
+        <v>1805400</v>
       </c>
       <c r="F8" s="3">
-        <v>1759200</v>
+        <v>1783900</v>
       </c>
       <c r="G8" s="3">
-        <v>1380500</v>
+        <v>1399900</v>
       </c>
       <c r="H8" s="3">
-        <v>1142200</v>
+        <v>1158300</v>
       </c>
       <c r="I8" s="3">
-        <v>883900</v>
+        <v>896300</v>
       </c>
       <c r="J8" s="3">
-        <v>913400</v>
+        <v>926200</v>
       </c>
       <c r="K8" s="3">
         <v>839300</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>612200</v>
+        <v>620800</v>
       </c>
       <c r="E9" s="3">
-        <v>626700</v>
+        <v>635500</v>
       </c>
       <c r="F9" s="3">
-        <v>646700</v>
+        <v>655800</v>
       </c>
       <c r="G9" s="3">
-        <v>541000</v>
+        <v>548600</v>
       </c>
       <c r="H9" s="3">
-        <v>552100</v>
+        <v>559900</v>
       </c>
       <c r="I9" s="3">
-        <v>495100</v>
+        <v>502100</v>
       </c>
       <c r="J9" s="3">
-        <v>561600</v>
+        <v>569500</v>
       </c>
       <c r="K9" s="3">
         <v>522100</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1037400</v>
+        <v>1051900</v>
       </c>
       <c r="E10" s="3">
-        <v>1153700</v>
+        <v>1169900</v>
       </c>
       <c r="F10" s="3">
-        <v>1112500</v>
+        <v>1128100</v>
       </c>
       <c r="G10" s="3">
-        <v>839500</v>
+        <v>851300</v>
       </c>
       <c r="H10" s="3">
-        <v>590100</v>
+        <v>598400</v>
       </c>
       <c r="I10" s="3">
-        <v>388800</v>
+        <v>394200</v>
       </c>
       <c r="J10" s="3">
-        <v>351800</v>
+        <v>356800</v>
       </c>
       <c r="K10" s="3">
         <v>317200</v>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1587700</v>
+        <v>1610000</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-92000</v>
+        <v>-93300</v>
       </c>
       <c r="G14" s="3">
-        <v>354700</v>
+        <v>359700</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>102800</v>
+        <v>104300</v>
       </c>
       <c r="J14" s="3">
-        <v>6100</v>
+        <v>6200</v>
       </c>
       <c r="K14" s="3">
         <v>73500</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2228700</v>
+        <v>2260000</v>
       </c>
       <c r="E17" s="3">
-        <v>669800</v>
+        <v>679200</v>
       </c>
       <c r="F17" s="3">
-        <v>594500</v>
+        <v>602800</v>
       </c>
       <c r="G17" s="3">
-        <v>925200</v>
+        <v>938200</v>
       </c>
       <c r="H17" s="3">
-        <v>587200</v>
+        <v>595400</v>
       </c>
       <c r="I17" s="3">
-        <v>628400</v>
+        <v>637200</v>
       </c>
       <c r="J17" s="3">
-        <v>601000</v>
+        <v>609400</v>
       </c>
       <c r="K17" s="3">
         <v>625600</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-579200</v>
+        <v>-587300</v>
       </c>
       <c r="E18" s="3">
-        <v>1110600</v>
+        <v>1126200</v>
       </c>
       <c r="F18" s="3">
-        <v>1164700</v>
+        <v>1181100</v>
       </c>
       <c r="G18" s="3">
-        <v>455400</v>
+        <v>461700</v>
       </c>
       <c r="H18" s="3">
-        <v>555100</v>
+        <v>562900</v>
       </c>
       <c r="I18" s="3">
-        <v>255500</v>
+        <v>259100</v>
       </c>
       <c r="J18" s="3">
-        <v>312500</v>
+        <v>316800</v>
       </c>
       <c r="K18" s="3">
         <v>213800</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>87100</v>
+        <v>88400</v>
       </c>
       <c r="E20" s="3">
-        <v>18900</v>
+        <v>19200</v>
       </c>
       <c r="F20" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="G20" s="3">
         <v>6000</v>
       </c>
       <c r="H20" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="K20" s="3">
         <v>17200</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-124200</v>
+        <v>-123200</v>
       </c>
       <c r="E21" s="3">
-        <v>1515000</v>
+        <v>1539100</v>
       </c>
       <c r="F21" s="3">
-        <v>1566200</v>
+        <v>1591200</v>
       </c>
       <c r="G21" s="3">
-        <v>785900</v>
+        <v>799300</v>
       </c>
       <c r="H21" s="3">
-        <v>915300</v>
+        <v>930700</v>
       </c>
       <c r="I21" s="3">
-        <v>589500</v>
+        <v>600200</v>
       </c>
       <c r="J21" s="3">
-        <v>687100</v>
+        <v>699400</v>
       </c>
       <c r="K21" s="3">
         <v>605500</v>
@@ -1170,7 +1170,7 @@
         <v>1900</v>
       </c>
       <c r="H22" s="3">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-492800</v>
+        <v>-499800</v>
       </c>
       <c r="E23" s="3">
-        <v>1128200</v>
+        <v>1144000</v>
       </c>
       <c r="F23" s="3">
-        <v>1160800</v>
+        <v>1177100</v>
       </c>
       <c r="G23" s="3">
-        <v>459400</v>
+        <v>465900</v>
       </c>
       <c r="H23" s="3">
-        <v>549300</v>
+        <v>557000</v>
       </c>
       <c r="I23" s="3">
-        <v>255900</v>
+        <v>259500</v>
       </c>
       <c r="J23" s="3">
-        <v>319400</v>
+        <v>323800</v>
       </c>
       <c r="K23" s="3">
         <v>230900</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>138300</v>
+        <v>140200</v>
       </c>
       <c r="E24" s="3">
-        <v>180100</v>
+        <v>182600</v>
       </c>
       <c r="F24" s="3">
-        <v>167900</v>
+        <v>170300</v>
       </c>
       <c r="G24" s="3">
-        <v>18000</v>
+        <v>18300</v>
       </c>
       <c r="H24" s="3">
-        <v>83600</v>
+        <v>84800</v>
       </c>
       <c r="I24" s="3">
-        <v>65100</v>
+        <v>66000</v>
       </c>
       <c r="J24" s="3">
-        <v>46300</v>
+        <v>46900</v>
       </c>
       <c r="K24" s="3">
         <v>62900</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-631100</v>
+        <v>-640000</v>
       </c>
       <c r="E26" s="3">
-        <v>948100</v>
+        <v>961400</v>
       </c>
       <c r="F26" s="3">
-        <v>992800</v>
+        <v>1006800</v>
       </c>
       <c r="G26" s="3">
-        <v>441400</v>
+        <v>447600</v>
       </c>
       <c r="H26" s="3">
-        <v>465600</v>
+        <v>472200</v>
       </c>
       <c r="I26" s="3">
-        <v>190800</v>
+        <v>193500</v>
       </c>
       <c r="J26" s="3">
-        <v>273100</v>
+        <v>276900</v>
       </c>
       <c r="K26" s="3">
         <v>168100</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-631100</v>
+        <v>-640000</v>
       </c>
       <c r="E27" s="3">
-        <v>948100</v>
+        <v>961400</v>
       </c>
       <c r="F27" s="3">
-        <v>992800</v>
+        <v>1006800</v>
       </c>
       <c r="G27" s="3">
-        <v>441400</v>
+        <v>447600</v>
       </c>
       <c r="H27" s="3">
-        <v>465600</v>
+        <v>472200</v>
       </c>
       <c r="I27" s="3">
-        <v>190800</v>
+        <v>193500</v>
       </c>
       <c r="J27" s="3">
-        <v>273100</v>
+        <v>276900</v>
       </c>
       <c r="K27" s="3">
         <v>168100</v>
@@ -1428,7 +1428,7 @@
         <v>-2700</v>
       </c>
       <c r="J29" s="3">
-        <v>-9600</v>
+        <v>-9700</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-87100</v>
+        <v>-88400</v>
       </c>
       <c r="E32" s="3">
-        <v>-18900</v>
+        <v>-19200</v>
       </c>
       <c r="F32" s="3">
-        <v>2000</v>
+        <v>2100</v>
       </c>
       <c r="G32" s="3">
         <v>-6000</v>
       </c>
       <c r="H32" s="3">
-        <v>-5700</v>
+        <v>-5800</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="K32" s="3">
         <v>-17200</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-631100</v>
+        <v>-640000</v>
       </c>
       <c r="E33" s="3">
-        <v>948100</v>
+        <v>961400</v>
       </c>
       <c r="F33" s="3">
-        <v>992800</v>
+        <v>1006800</v>
       </c>
       <c r="G33" s="3">
-        <v>441400</v>
+        <v>447600</v>
       </c>
       <c r="H33" s="3">
-        <v>465600</v>
+        <v>472200</v>
       </c>
       <c r="I33" s="3">
-        <v>188100</v>
+        <v>190700</v>
       </c>
       <c r="J33" s="3">
-        <v>263500</v>
+        <v>267200</v>
       </c>
       <c r="K33" s="3">
         <v>168100</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-631100</v>
+        <v>-640000</v>
       </c>
       <c r="E35" s="3">
-        <v>948100</v>
+        <v>961400</v>
       </c>
       <c r="F35" s="3">
-        <v>992800</v>
+        <v>1006800</v>
       </c>
       <c r="G35" s="3">
-        <v>441400</v>
+        <v>447600</v>
       </c>
       <c r="H35" s="3">
-        <v>465600</v>
+        <v>472200</v>
       </c>
       <c r="I35" s="3">
-        <v>188100</v>
+        <v>190700</v>
       </c>
       <c r="J35" s="3">
-        <v>263500</v>
+        <v>267200</v>
       </c>
       <c r="K35" s="3">
         <v>168100</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1924100</v>
+        <v>1951100</v>
       </c>
       <c r="E41" s="3">
-        <v>1619100</v>
+        <v>1641800</v>
       </c>
       <c r="F41" s="3">
-        <v>729800</v>
+        <v>740000</v>
       </c>
       <c r="G41" s="3">
-        <v>722900</v>
+        <v>733000</v>
       </c>
       <c r="H41" s="3">
-        <v>178800</v>
+        <v>181300</v>
       </c>
       <c r="I41" s="3">
-        <v>94300</v>
+        <v>95600</v>
       </c>
       <c r="J41" s="3">
-        <v>691600</v>
+        <v>701300</v>
       </c>
       <c r="K41" s="3">
         <v>348000</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>150200</v>
+        <v>152300</v>
       </c>
       <c r="E43" s="3">
-        <v>183600</v>
+        <v>186200</v>
       </c>
       <c r="F43" s="3">
-        <v>215800</v>
+        <v>218900</v>
       </c>
       <c r="G43" s="3">
-        <v>126400</v>
+        <v>128200</v>
       </c>
       <c r="H43" s="3">
-        <v>132300</v>
+        <v>134200</v>
       </c>
       <c r="I43" s="3">
-        <v>102200</v>
+        <v>103600</v>
       </c>
       <c r="J43" s="3">
-        <v>89200</v>
+        <v>90400</v>
       </c>
       <c r="K43" s="3">
         <v>97800</v>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>9600</v>
+        <v>9700</v>
       </c>
       <c r="K44" s="3">
         <v>3700</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>111500</v>
+        <v>113100</v>
       </c>
       <c r="E45" s="3">
-        <v>68900</v>
+        <v>69800</v>
       </c>
       <c r="F45" s="3">
-        <v>71200</v>
+        <v>72200</v>
       </c>
       <c r="G45" s="3">
-        <v>48900</v>
+        <v>49500</v>
       </c>
       <c r="H45" s="3">
-        <v>66000</v>
+        <v>67000</v>
       </c>
       <c r="I45" s="3">
-        <v>45100</v>
+        <v>45700</v>
       </c>
       <c r="J45" s="3">
-        <v>43700</v>
+        <v>44300</v>
       </c>
       <c r="K45" s="3">
         <v>47300</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2185800</v>
+        <v>2216500</v>
       </c>
       <c r="E46" s="3">
-        <v>1871600</v>
+        <v>1897900</v>
       </c>
       <c r="F46" s="3">
-        <v>1016800</v>
+        <v>1031100</v>
       </c>
       <c r="G46" s="3">
-        <v>898100</v>
+        <v>910700</v>
       </c>
       <c r="H46" s="3">
-        <v>377100</v>
+        <v>382400</v>
       </c>
       <c r="I46" s="3">
-        <v>241500</v>
+        <v>244900</v>
       </c>
       <c r="J46" s="3">
-        <v>834100</v>
+        <v>845800</v>
       </c>
       <c r="K46" s="3">
         <v>496800</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>367000</v>
+        <v>372100</v>
       </c>
       <c r="E47" s="3">
-        <v>303900</v>
+        <v>308200</v>
       </c>
       <c r="F47" s="3">
-        <v>318100</v>
+        <v>322600</v>
       </c>
       <c r="G47" s="3">
-        <v>314900</v>
+        <v>319300</v>
       </c>
       <c r="H47" s="3">
-        <v>243800</v>
+        <v>247300</v>
       </c>
       <c r="I47" s="3">
-        <v>228700</v>
+        <v>231900</v>
       </c>
       <c r="J47" s="3">
-        <v>273800</v>
+        <v>277600</v>
       </c>
       <c r="K47" s="3">
         <v>201500</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5458400</v>
+        <v>5535000</v>
       </c>
       <c r="E48" s="3">
-        <v>6677000</v>
+        <v>6770700</v>
       </c>
       <c r="F48" s="3">
-        <v>6977600</v>
+        <v>7075600</v>
       </c>
       <c r="G48" s="3">
-        <v>6278200</v>
+        <v>6366300</v>
       </c>
       <c r="H48" s="3">
-        <v>6508900</v>
+        <v>6600300</v>
       </c>
       <c r="I48" s="3">
-        <v>6179100</v>
+        <v>6265900</v>
       </c>
       <c r="J48" s="3">
-        <v>5348500</v>
+        <v>5423600</v>
       </c>
       <c r="K48" s="3">
         <v>5066000</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100000</v>
+        <v>101400</v>
       </c>
       <c r="E52" s="3">
-        <v>114900</v>
+        <v>116500</v>
       </c>
       <c r="F52" s="3">
-        <v>90700</v>
+        <v>91900</v>
       </c>
       <c r="G52" s="3">
-        <v>77100</v>
+        <v>78200</v>
       </c>
       <c r="H52" s="3">
-        <v>15800</v>
+        <v>16100</v>
       </c>
       <c r="I52" s="3">
-        <v>24400</v>
+        <v>24700</v>
       </c>
       <c r="J52" s="3">
-        <v>23300</v>
+        <v>23600</v>
       </c>
       <c r="K52" s="3">
         <v>42500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8111200</v>
+        <v>8225100</v>
       </c>
       <c r="E54" s="3">
-        <v>8967400</v>
+        <v>9093300</v>
       </c>
       <c r="F54" s="3">
-        <v>8403200</v>
+        <v>8521200</v>
       </c>
       <c r="G54" s="3">
-        <v>7568300</v>
+        <v>7674600</v>
       </c>
       <c r="H54" s="3">
-        <v>7145700</v>
+        <v>7246000</v>
       </c>
       <c r="I54" s="3">
-        <v>6673700</v>
+        <v>6767400</v>
       </c>
       <c r="J54" s="3">
-        <v>6479700</v>
+        <v>6570600</v>
       </c>
       <c r="K54" s="3">
         <v>5806800</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7400</v>
+        <v>7500</v>
       </c>
       <c r="E57" s="3">
-        <v>9500</v>
+        <v>9600</v>
       </c>
       <c r="F57" s="3">
-        <v>11500</v>
+        <v>11700</v>
       </c>
       <c r="G57" s="3">
-        <v>4700</v>
+        <v>4800</v>
       </c>
       <c r="H57" s="3">
-        <v>9200</v>
+        <v>9300</v>
       </c>
       <c r="I57" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="J57" s="3">
-        <v>8400</v>
+        <v>8500</v>
       </c>
       <c r="K57" s="3">
         <v>13200</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45600</v>
+        <v>46200</v>
       </c>
       <c r="E59" s="3">
-        <v>58500</v>
+        <v>59300</v>
       </c>
       <c r="F59" s="3">
-        <v>47000</v>
+        <v>47600</v>
       </c>
       <c r="G59" s="3">
-        <v>67300</v>
+        <v>68200</v>
       </c>
       <c r="H59" s="3">
-        <v>63100</v>
+        <v>63900</v>
       </c>
       <c r="I59" s="3">
-        <v>24000</v>
+        <v>24300</v>
       </c>
       <c r="J59" s="3">
-        <v>22200</v>
+        <v>22500</v>
       </c>
       <c r="K59" s="3">
         <v>38500</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53000</v>
+        <v>53800</v>
       </c>
       <c r="E60" s="3">
-        <v>67900</v>
+        <v>68900</v>
       </c>
       <c r="F60" s="3">
-        <v>58500</v>
+        <v>59300</v>
       </c>
       <c r="G60" s="3">
-        <v>72000</v>
+        <v>73000</v>
       </c>
       <c r="H60" s="3">
-        <v>72300</v>
+        <v>73300</v>
       </c>
       <c r="I60" s="3">
-        <v>33800</v>
+        <v>34300</v>
       </c>
       <c r="J60" s="3">
-        <v>30600</v>
+        <v>31000</v>
       </c>
       <c r="K60" s="3">
         <v>51700</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>111800</v>
+        <v>113300</v>
       </c>
       <c r="I61" s="3">
-        <v>280900</v>
+        <v>284900</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>251400</v>
+        <v>255000</v>
       </c>
       <c r="E62" s="3">
-        <v>215200</v>
+        <v>218200</v>
       </c>
       <c r="F62" s="3">
-        <v>191500</v>
+        <v>194200</v>
       </c>
       <c r="G62" s="3">
-        <v>129800</v>
+        <v>131600</v>
       </c>
       <c r="H62" s="3">
-        <v>111500</v>
+        <v>113100</v>
       </c>
       <c r="I62" s="3">
-        <v>91100</v>
+        <v>92300</v>
       </c>
       <c r="J62" s="3">
-        <v>81600</v>
+        <v>82700</v>
       </c>
       <c r="K62" s="3">
         <v>51600</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>304500</v>
+        <v>308700</v>
       </c>
       <c r="E66" s="3">
-        <v>283100</v>
+        <v>287100</v>
       </c>
       <c r="F66" s="3">
-        <v>249900</v>
+        <v>253400</v>
       </c>
       <c r="G66" s="3">
-        <v>201800</v>
+        <v>204600</v>
       </c>
       <c r="H66" s="3">
-        <v>295500</v>
+        <v>299700</v>
       </c>
       <c r="I66" s="3">
-        <v>405800</v>
+        <v>411500</v>
       </c>
       <c r="J66" s="3">
-        <v>112200</v>
+        <v>113800</v>
       </c>
       <c r="K66" s="3">
         <v>103300</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>287300</v>
+        <v>291300</v>
       </c>
       <c r="E72" s="3">
-        <v>1272500</v>
+        <v>1290400</v>
       </c>
       <c r="F72" s="3">
-        <v>656200</v>
+        <v>665400</v>
       </c>
       <c r="G72" s="3">
-        <v>-46600</v>
+        <v>-47200</v>
       </c>
       <c r="H72" s="3">
-        <v>-222500</v>
+        <v>-225600</v>
       </c>
       <c r="I72" s="3">
-        <v>-435300</v>
+        <v>-441400</v>
       </c>
       <c r="J72" s="3">
-        <v>-419500</v>
+        <v>-425400</v>
       </c>
       <c r="K72" s="3">
         <v>-463300</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7806700</v>
+        <v>7916400</v>
       </c>
       <c r="E76" s="3">
-        <v>8684300</v>
+        <v>8806200</v>
       </c>
       <c r="F76" s="3">
-        <v>8153300</v>
+        <v>8267800</v>
       </c>
       <c r="G76" s="3">
-        <v>7366600</v>
+        <v>7470000</v>
       </c>
       <c r="H76" s="3">
-        <v>6850200</v>
+        <v>6946400</v>
       </c>
       <c r="I76" s="3">
-        <v>6267900</v>
+        <v>6355900</v>
       </c>
       <c r="J76" s="3">
-        <v>6367500</v>
+        <v>6456900</v>
       </c>
       <c r="K76" s="3">
         <v>5703500</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-631100</v>
+        <v>-640000</v>
       </c>
       <c r="E81" s="3">
-        <v>948100</v>
+        <v>961400</v>
       </c>
       <c r="F81" s="3">
-        <v>992800</v>
+        <v>1006800</v>
       </c>
       <c r="G81" s="3">
-        <v>441400</v>
+        <v>447600</v>
       </c>
       <c r="H81" s="3">
-        <v>465600</v>
+        <v>472200</v>
       </c>
       <c r="I81" s="3">
-        <v>188100</v>
+        <v>190700</v>
       </c>
       <c r="J81" s="3">
-        <v>263500</v>
+        <v>267200</v>
       </c>
       <c r="K81" s="3">
         <v>168100</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>369600</v>
+        <v>374700</v>
       </c>
       <c r="E83" s="3">
-        <v>387300</v>
+        <v>392700</v>
       </c>
       <c r="F83" s="3">
-        <v>405400</v>
+        <v>411100</v>
       </c>
       <c r="G83" s="3">
-        <v>326100</v>
+        <v>330700</v>
       </c>
       <c r="H83" s="3">
-        <v>356200</v>
+        <v>361200</v>
       </c>
       <c r="I83" s="3">
-        <v>335200</v>
+        <v>339900</v>
       </c>
       <c r="J83" s="3">
-        <v>369400</v>
+        <v>374600</v>
       </c>
       <c r="K83" s="3">
         <v>376600</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1341300</v>
+        <v>1360100</v>
       </c>
       <c r="E89" s="3">
-        <v>1352500</v>
+        <v>1371500</v>
       </c>
       <c r="F89" s="3">
-        <v>1292800</v>
+        <v>1311000</v>
       </c>
       <c r="G89" s="3">
-        <v>1087800</v>
+        <v>1103100</v>
       </c>
       <c r="H89" s="3">
-        <v>835900</v>
+        <v>847600</v>
       </c>
       <c r="I89" s="3">
-        <v>642500</v>
+        <v>651500</v>
       </c>
       <c r="J89" s="3">
-        <v>661200</v>
+        <v>670500</v>
       </c>
       <c r="K89" s="3">
         <v>647900</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-705800</v>
+        <v>-715700</v>
       </c>
       <c r="E91" s="3">
-        <v>-191500</v>
+        <v>-194200</v>
       </c>
       <c r="F91" s="3">
-        <v>-1029100</v>
+        <v>-1043600</v>
       </c>
       <c r="G91" s="3">
-        <v>-423000</v>
+        <v>-428900</v>
       </c>
       <c r="H91" s="3">
-        <v>-602400</v>
+        <v>-610900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1339100</v>
+        <v>-1357900</v>
       </c>
       <c r="J91" s="3">
-        <v>-678200</v>
+        <v>-687700</v>
       </c>
       <c r="K91" s="3">
         <v>-1027600</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-732200</v>
+        <v>-742500</v>
       </c>
       <c r="E94" s="3">
-        <v>-196900</v>
+        <v>-199700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1035200</v>
+        <v>-1049700</v>
       </c>
       <c r="G94" s="3">
-        <v>-418100</v>
+        <v>-424000</v>
       </c>
       <c r="H94" s="3">
-        <v>-590100</v>
+        <v>-598400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1337900</v>
+        <v>-1356700</v>
       </c>
       <c r="J94" s="3">
-        <v>-677800</v>
+        <v>-687300</v>
       </c>
       <c r="K94" s="3">
         <v>-948800</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-315300</v>
+        <v>-319700</v>
       </c>
       <c r="E96" s="3">
-        <v>-267400</v>
+        <v>-271100</v>
       </c>
       <c r="F96" s="3">
-        <v>-243000</v>
+        <v>-246400</v>
       </c>
       <c r="G96" s="3">
-        <v>-209600</v>
+        <v>-212600</v>
       </c>
       <c r="H96" s="3">
-        <v>-187000</v>
+        <v>-189600</v>
       </c>
       <c r="I96" s="3">
-        <v>-184200</v>
+        <v>-186800</v>
       </c>
       <c r="J96" s="3">
-        <v>-170200</v>
+        <v>-172600</v>
       </c>
       <c r="K96" s="3">
         <v>-162400</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-311400</v>
+        <v>-315700</v>
       </c>
       <c r="E100" s="3">
-        <v>-255800</v>
+        <v>-259300</v>
       </c>
       <c r="F100" s="3">
-        <v>-243800</v>
+        <v>-247300</v>
       </c>
       <c r="G100" s="3">
-        <v>-124200</v>
+        <v>-126000</v>
       </c>
       <c r="H100" s="3">
-        <v>-162100</v>
+        <v>-164400</v>
       </c>
       <c r="I100" s="3">
-        <v>105000</v>
+        <v>106500</v>
       </c>
       <c r="J100" s="3">
-        <v>324400</v>
+        <v>328900</v>
       </c>
       <c r="K100" s="3">
         <v>442500</v>
@@ -3708,13 +3708,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7300</v>
+        <v>7400</v>
       </c>
       <c r="E101" s="3">
-        <v>-10600</v>
+        <v>-10700</v>
       </c>
       <c r="F101" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="G101" s="3">
         <v>-1400</v>
@@ -3723,10 +3723,10 @@
         <v>800</v>
       </c>
       <c r="I101" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="J101" s="3">
-        <v>41500</v>
+        <v>42100</v>
       </c>
       <c r="K101" s="3">
         <v>1200</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>305000</v>
+        <v>309300</v>
       </c>
       <c r="E102" s="3">
-        <v>889300</v>
+        <v>901800</v>
       </c>
       <c r="F102" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="G102" s="3">
-        <v>544100</v>
+        <v>551800</v>
       </c>
       <c r="H102" s="3">
-        <v>84400</v>
+        <v>85600</v>
       </c>
       <c r="I102" s="3">
-        <v>-597300</v>
+        <v>-605700</v>
       </c>
       <c r="J102" s="3">
-        <v>349300</v>
+        <v>354200</v>
       </c>
       <c r="K102" s="3">
         <v>142800</v>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1672700</v>
+        <v>1656000</v>
       </c>
       <c r="E8" s="3">
-        <v>1805400</v>
+        <v>1787400</v>
       </c>
       <c r="F8" s="3">
-        <v>1783900</v>
+        <v>1766100</v>
       </c>
       <c r="G8" s="3">
-        <v>1399900</v>
+        <v>1385900</v>
       </c>
       <c r="H8" s="3">
-        <v>1158300</v>
+        <v>1146700</v>
       </c>
       <c r="I8" s="3">
-        <v>896300</v>
+        <v>887400</v>
       </c>
       <c r="J8" s="3">
-        <v>926200</v>
+        <v>917000</v>
       </c>
       <c r="K8" s="3">
         <v>839300</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>620800</v>
+        <v>614600</v>
       </c>
       <c r="E9" s="3">
-        <v>635500</v>
+        <v>629100</v>
       </c>
       <c r="F9" s="3">
-        <v>655800</v>
+        <v>649200</v>
       </c>
       <c r="G9" s="3">
-        <v>548600</v>
+        <v>543100</v>
       </c>
       <c r="H9" s="3">
-        <v>559900</v>
+        <v>554300</v>
       </c>
       <c r="I9" s="3">
-        <v>502100</v>
+        <v>497100</v>
       </c>
       <c r="J9" s="3">
-        <v>569500</v>
+        <v>563800</v>
       </c>
       <c r="K9" s="3">
         <v>522100</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1051900</v>
+        <v>1041400</v>
       </c>
       <c r="E10" s="3">
-        <v>1169900</v>
+        <v>1158300</v>
       </c>
       <c r="F10" s="3">
-        <v>1128100</v>
+        <v>1116800</v>
       </c>
       <c r="G10" s="3">
-        <v>851300</v>
+        <v>842800</v>
       </c>
       <c r="H10" s="3">
-        <v>598400</v>
+        <v>592400</v>
       </c>
       <c r="I10" s="3">
-        <v>394200</v>
+        <v>390300</v>
       </c>
       <c r="J10" s="3">
-        <v>356800</v>
+        <v>353200</v>
       </c>
       <c r="K10" s="3">
         <v>317200</v>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1610000</v>
+        <v>1593900</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
-        <v>-93300</v>
+        <v>-92400</v>
       </c>
       <c r="G14" s="3">
-        <v>359700</v>
+        <v>356100</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>104300</v>
+        <v>103200</v>
       </c>
       <c r="J14" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="K14" s="3">
         <v>73500</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2260000</v>
+        <v>2237400</v>
       </c>
       <c r="E17" s="3">
-        <v>679200</v>
+        <v>672500</v>
       </c>
       <c r="F17" s="3">
-        <v>602800</v>
+        <v>596800</v>
       </c>
       <c r="G17" s="3">
-        <v>938200</v>
+        <v>928800</v>
       </c>
       <c r="H17" s="3">
-        <v>595400</v>
+        <v>589500</v>
       </c>
       <c r="I17" s="3">
-        <v>637200</v>
+        <v>630900</v>
       </c>
       <c r="J17" s="3">
-        <v>609400</v>
+        <v>603300</v>
       </c>
       <c r="K17" s="3">
         <v>625600</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-587300</v>
+        <v>-581400</v>
       </c>
       <c r="E18" s="3">
-        <v>1126200</v>
+        <v>1114900</v>
       </c>
       <c r="F18" s="3">
-        <v>1181100</v>
+        <v>1169300</v>
       </c>
       <c r="G18" s="3">
-        <v>461700</v>
+        <v>457100</v>
       </c>
       <c r="H18" s="3">
-        <v>562900</v>
+        <v>557300</v>
       </c>
       <c r="I18" s="3">
-        <v>259100</v>
+        <v>256500</v>
       </c>
       <c r="J18" s="3">
-        <v>316800</v>
+        <v>313700</v>
       </c>
       <c r="K18" s="3">
         <v>213800</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>88400</v>
+        <v>87500</v>
       </c>
       <c r="E20" s="3">
-        <v>19200</v>
+        <v>19000</v>
       </c>
       <c r="F20" s="3">
-        <v>-2100</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
         <v>6000</v>
       </c>
       <c r="H20" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="I20" s="3">
         <v>400</v>
       </c>
       <c r="J20" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="K20" s="3">
         <v>17200</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-123200</v>
+        <v>-123100</v>
       </c>
       <c r="E21" s="3">
-        <v>1539100</v>
+        <v>1522600</v>
       </c>
       <c r="F21" s="3">
-        <v>1591200</v>
+        <v>1574100</v>
       </c>
       <c r="G21" s="3">
-        <v>799300</v>
+        <v>790400</v>
       </c>
       <c r="H21" s="3">
-        <v>930700</v>
+        <v>920400</v>
       </c>
       <c r="I21" s="3">
-        <v>600200</v>
+        <v>593300</v>
       </c>
       <c r="J21" s="3">
-        <v>699400</v>
+        <v>691300</v>
       </c>
       <c r="K21" s="3">
         <v>605500</v>
@@ -1170,7 +1170,7 @@
         <v>1900</v>
       </c>
       <c r="H22" s="3">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>8</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-499800</v>
+        <v>-494800</v>
       </c>
       <c r="E23" s="3">
-        <v>1144000</v>
+        <v>1132600</v>
       </c>
       <c r="F23" s="3">
-        <v>1177100</v>
+        <v>1165300</v>
       </c>
       <c r="G23" s="3">
-        <v>465900</v>
+        <v>461200</v>
       </c>
       <c r="H23" s="3">
-        <v>557000</v>
+        <v>551400</v>
       </c>
       <c r="I23" s="3">
-        <v>259500</v>
+        <v>256900</v>
       </c>
       <c r="J23" s="3">
-        <v>323800</v>
+        <v>320600</v>
       </c>
       <c r="K23" s="3">
         <v>230900</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>140200</v>
+        <v>138800</v>
       </c>
       <c r="E24" s="3">
-        <v>182600</v>
+        <v>180800</v>
       </c>
       <c r="F24" s="3">
-        <v>170300</v>
+        <v>168600</v>
       </c>
       <c r="G24" s="3">
-        <v>18300</v>
+        <v>18100</v>
       </c>
       <c r="H24" s="3">
-        <v>84800</v>
+        <v>84000</v>
       </c>
       <c r="I24" s="3">
-        <v>66000</v>
+        <v>65300</v>
       </c>
       <c r="J24" s="3">
-        <v>46900</v>
+        <v>46500</v>
       </c>
       <c r="K24" s="3">
         <v>62900</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-640000</v>
+        <v>-633600</v>
       </c>
       <c r="E26" s="3">
-        <v>961400</v>
+        <v>951800</v>
       </c>
       <c r="F26" s="3">
-        <v>1006800</v>
+        <v>996700</v>
       </c>
       <c r="G26" s="3">
-        <v>447600</v>
+        <v>443100</v>
       </c>
       <c r="H26" s="3">
-        <v>472200</v>
+        <v>467500</v>
       </c>
       <c r="I26" s="3">
-        <v>193500</v>
+        <v>191500</v>
       </c>
       <c r="J26" s="3">
-        <v>276900</v>
+        <v>274100</v>
       </c>
       <c r="K26" s="3">
         <v>168100</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-640000</v>
+        <v>-633600</v>
       </c>
       <c r="E27" s="3">
-        <v>961400</v>
+        <v>951800</v>
       </c>
       <c r="F27" s="3">
-        <v>1006800</v>
+        <v>996700</v>
       </c>
       <c r="G27" s="3">
-        <v>447600</v>
+        <v>443100</v>
       </c>
       <c r="H27" s="3">
-        <v>472200</v>
+        <v>467500</v>
       </c>
       <c r="I27" s="3">
-        <v>193500</v>
+        <v>191500</v>
       </c>
       <c r="J27" s="3">
-        <v>276900</v>
+        <v>274100</v>
       </c>
       <c r="K27" s="3">
         <v>168100</v>
@@ -1428,7 +1428,7 @@
         <v>-2700</v>
       </c>
       <c r="J29" s="3">
-        <v>-9700</v>
+        <v>-9600</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-88400</v>
+        <v>-87500</v>
       </c>
       <c r="E32" s="3">
-        <v>-19200</v>
+        <v>-19000</v>
       </c>
       <c r="F32" s="3">
-        <v>2100</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
         <v>-6000</v>
       </c>
       <c r="H32" s="3">
-        <v>-5800</v>
+        <v>-5700</v>
       </c>
       <c r="I32" s="3">
         <v>-400</v>
       </c>
       <c r="J32" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="K32" s="3">
         <v>-17200</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-640000</v>
+        <v>-633600</v>
       </c>
       <c r="E33" s="3">
-        <v>961400</v>
+        <v>951800</v>
       </c>
       <c r="F33" s="3">
-        <v>1006800</v>
+        <v>996700</v>
       </c>
       <c r="G33" s="3">
-        <v>447600</v>
+        <v>443100</v>
       </c>
       <c r="H33" s="3">
-        <v>472200</v>
+        <v>467500</v>
       </c>
       <c r="I33" s="3">
-        <v>190700</v>
+        <v>188800</v>
       </c>
       <c r="J33" s="3">
-        <v>267200</v>
+        <v>264500</v>
       </c>
       <c r="K33" s="3">
         <v>168100</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-640000</v>
+        <v>-633600</v>
       </c>
       <c r="E35" s="3">
-        <v>961400</v>
+        <v>951800</v>
       </c>
       <c r="F35" s="3">
-        <v>1006800</v>
+        <v>996700</v>
       </c>
       <c r="G35" s="3">
-        <v>447600</v>
+        <v>443100</v>
       </c>
       <c r="H35" s="3">
-        <v>472200</v>
+        <v>467500</v>
       </c>
       <c r="I35" s="3">
-        <v>190700</v>
+        <v>188800</v>
       </c>
       <c r="J35" s="3">
-        <v>267200</v>
+        <v>264500</v>
       </c>
       <c r="K35" s="3">
         <v>168100</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1951100</v>
+        <v>1931700</v>
       </c>
       <c r="E41" s="3">
-        <v>1641800</v>
+        <v>1625400</v>
       </c>
       <c r="F41" s="3">
-        <v>740000</v>
+        <v>732600</v>
       </c>
       <c r="G41" s="3">
-        <v>733000</v>
+        <v>725700</v>
       </c>
       <c r="H41" s="3">
-        <v>181300</v>
+        <v>179500</v>
       </c>
       <c r="I41" s="3">
-        <v>95600</v>
+        <v>94700</v>
       </c>
       <c r="J41" s="3">
-        <v>701300</v>
+        <v>694300</v>
       </c>
       <c r="K41" s="3">
         <v>348000</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>152300</v>
+        <v>150800</v>
       </c>
       <c r="E43" s="3">
-        <v>186200</v>
+        <v>184300</v>
       </c>
       <c r="F43" s="3">
-        <v>218900</v>
+        <v>216700</v>
       </c>
       <c r="G43" s="3">
-        <v>128200</v>
+        <v>126900</v>
       </c>
       <c r="H43" s="3">
-        <v>134200</v>
+        <v>132900</v>
       </c>
       <c r="I43" s="3">
-        <v>103600</v>
+        <v>102600</v>
       </c>
       <c r="J43" s="3">
-        <v>90400</v>
+        <v>89500</v>
       </c>
       <c r="K43" s="3">
         <v>97800</v>
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="3">
-        <v>9700</v>
+        <v>9600</v>
       </c>
       <c r="K44" s="3">
         <v>3700</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>113100</v>
+        <v>111900</v>
       </c>
       <c r="E45" s="3">
-        <v>69800</v>
+        <v>69100</v>
       </c>
       <c r="F45" s="3">
-        <v>72200</v>
+        <v>71500</v>
       </c>
       <c r="G45" s="3">
-        <v>49500</v>
+        <v>49000</v>
       </c>
       <c r="H45" s="3">
-        <v>67000</v>
+        <v>66300</v>
       </c>
       <c r="I45" s="3">
-        <v>45700</v>
+        <v>45200</v>
       </c>
       <c r="J45" s="3">
-        <v>44300</v>
+        <v>43900</v>
       </c>
       <c r="K45" s="3">
         <v>47300</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2216500</v>
+        <v>2194400</v>
       </c>
       <c r="E46" s="3">
-        <v>1897900</v>
+        <v>1878900</v>
       </c>
       <c r="F46" s="3">
-        <v>1031100</v>
+        <v>1020800</v>
       </c>
       <c r="G46" s="3">
-        <v>910700</v>
+        <v>901600</v>
       </c>
       <c r="H46" s="3">
-        <v>382400</v>
+        <v>378600</v>
       </c>
       <c r="I46" s="3">
-        <v>244900</v>
+        <v>242500</v>
       </c>
       <c r="J46" s="3">
-        <v>845800</v>
+        <v>837400</v>
       </c>
       <c r="K46" s="3">
         <v>496800</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>372100</v>
+        <v>368400</v>
       </c>
       <c r="E47" s="3">
-        <v>308200</v>
+        <v>305100</v>
       </c>
       <c r="F47" s="3">
-        <v>322600</v>
+        <v>319400</v>
       </c>
       <c r="G47" s="3">
-        <v>319300</v>
+        <v>316100</v>
       </c>
       <c r="H47" s="3">
-        <v>247300</v>
+        <v>244800</v>
       </c>
       <c r="I47" s="3">
-        <v>231900</v>
+        <v>229600</v>
       </c>
       <c r="J47" s="3">
-        <v>277600</v>
+        <v>274800</v>
       </c>
       <c r="K47" s="3">
         <v>201500</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5535000</v>
+        <v>5479800</v>
       </c>
       <c r="E48" s="3">
-        <v>6770700</v>
+        <v>6703100</v>
       </c>
       <c r="F48" s="3">
-        <v>7075600</v>
+        <v>7005000</v>
       </c>
       <c r="G48" s="3">
-        <v>6366300</v>
+        <v>6302800</v>
       </c>
       <c r="H48" s="3">
-        <v>6600300</v>
+        <v>6534400</v>
       </c>
       <c r="I48" s="3">
-        <v>6265900</v>
+        <v>6203300</v>
       </c>
       <c r="J48" s="3">
-        <v>5423600</v>
+        <v>5369500</v>
       </c>
       <c r="K48" s="3">
         <v>5066000</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>101400</v>
+        <v>100400</v>
       </c>
       <c r="E52" s="3">
-        <v>116500</v>
+        <v>115300</v>
       </c>
       <c r="F52" s="3">
-        <v>91900</v>
+        <v>91000</v>
       </c>
       <c r="G52" s="3">
-        <v>78200</v>
+        <v>77400</v>
       </c>
       <c r="H52" s="3">
-        <v>16100</v>
+        <v>15900</v>
       </c>
       <c r="I52" s="3">
-        <v>24700</v>
+        <v>24500</v>
       </c>
       <c r="J52" s="3">
-        <v>23600</v>
+        <v>23400</v>
       </c>
       <c r="K52" s="3">
         <v>42500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8225100</v>
+        <v>8143000</v>
       </c>
       <c r="E54" s="3">
-        <v>9093300</v>
+        <v>9002500</v>
       </c>
       <c r="F54" s="3">
-        <v>8521200</v>
+        <v>8436100</v>
       </c>
       <c r="G54" s="3">
-        <v>7674600</v>
+        <v>7598000</v>
       </c>
       <c r="H54" s="3">
-        <v>7246000</v>
+        <v>7173700</v>
       </c>
       <c r="I54" s="3">
-        <v>6767400</v>
+        <v>6699900</v>
       </c>
       <c r="J54" s="3">
-        <v>6570600</v>
+        <v>6505000</v>
       </c>
       <c r="K54" s="3">
         <v>5806800</v>
@@ -2274,22 +2274,22 @@
         <v>7500</v>
       </c>
       <c r="E57" s="3">
-        <v>9600</v>
+        <v>9500</v>
       </c>
       <c r="F57" s="3">
-        <v>11700</v>
+        <v>11500</v>
       </c>
       <c r="G57" s="3">
         <v>4800</v>
       </c>
       <c r="H57" s="3">
-        <v>9300</v>
+        <v>9200</v>
       </c>
       <c r="I57" s="3">
-        <v>10000</v>
+        <v>9900</v>
       </c>
       <c r="J57" s="3">
-        <v>8500</v>
+        <v>8400</v>
       </c>
       <c r="K57" s="3">
         <v>13200</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>46200</v>
+        <v>45800</v>
       </c>
       <c r="E59" s="3">
-        <v>59300</v>
+        <v>58700</v>
       </c>
       <c r="F59" s="3">
-        <v>47600</v>
+        <v>47100</v>
       </c>
       <c r="G59" s="3">
-        <v>68200</v>
+        <v>67500</v>
       </c>
       <c r="H59" s="3">
-        <v>63900</v>
+        <v>63300</v>
       </c>
       <c r="I59" s="3">
-        <v>24300</v>
+        <v>24000</v>
       </c>
       <c r="J59" s="3">
-        <v>22500</v>
+        <v>22300</v>
       </c>
       <c r="K59" s="3">
         <v>38500</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53800</v>
+        <v>53300</v>
       </c>
       <c r="E60" s="3">
-        <v>68900</v>
+        <v>68200</v>
       </c>
       <c r="F60" s="3">
-        <v>59300</v>
+        <v>58700</v>
       </c>
       <c r="G60" s="3">
-        <v>73000</v>
+        <v>72300</v>
       </c>
       <c r="H60" s="3">
-        <v>73300</v>
+        <v>72500</v>
       </c>
       <c r="I60" s="3">
-        <v>34300</v>
+        <v>34000</v>
       </c>
       <c r="J60" s="3">
-        <v>31000</v>
+        <v>30700</v>
       </c>
       <c r="K60" s="3">
         <v>51700</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>113300</v>
+        <v>112200</v>
       </c>
       <c r="I61" s="3">
-        <v>284900</v>
+        <v>282000</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>255000</v>
+        <v>252400</v>
       </c>
       <c r="E62" s="3">
-        <v>218200</v>
+        <v>216000</v>
       </c>
       <c r="F62" s="3">
-        <v>194200</v>
+        <v>192200</v>
       </c>
       <c r="G62" s="3">
-        <v>131600</v>
+        <v>130300</v>
       </c>
       <c r="H62" s="3">
-        <v>113100</v>
+        <v>111900</v>
       </c>
       <c r="I62" s="3">
-        <v>92300</v>
+        <v>91400</v>
       </c>
       <c r="J62" s="3">
-        <v>82700</v>
+        <v>81900</v>
       </c>
       <c r="K62" s="3">
         <v>51600</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>308700</v>
+        <v>305700</v>
       </c>
       <c r="E66" s="3">
-        <v>287100</v>
+        <v>284200</v>
       </c>
       <c r="F66" s="3">
-        <v>253400</v>
+        <v>250900</v>
       </c>
       <c r="G66" s="3">
-        <v>204600</v>
+        <v>202600</v>
       </c>
       <c r="H66" s="3">
-        <v>299700</v>
+        <v>296700</v>
       </c>
       <c r="I66" s="3">
-        <v>411500</v>
+        <v>407400</v>
       </c>
       <c r="J66" s="3">
-        <v>113800</v>
+        <v>112600</v>
       </c>
       <c r="K66" s="3">
         <v>103300</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>291300</v>
+        <v>288400</v>
       </c>
       <c r="E72" s="3">
-        <v>1290400</v>
+        <v>1277500</v>
       </c>
       <c r="F72" s="3">
-        <v>665400</v>
+        <v>658700</v>
       </c>
       <c r="G72" s="3">
-        <v>-47200</v>
+        <v>-46700</v>
       </c>
       <c r="H72" s="3">
-        <v>-225600</v>
+        <v>-223300</v>
       </c>
       <c r="I72" s="3">
-        <v>-441400</v>
+        <v>-437000</v>
       </c>
       <c r="J72" s="3">
-        <v>-425400</v>
+        <v>-421100</v>
       </c>
       <c r="K72" s="3">
         <v>-463300</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7916400</v>
+        <v>7837300</v>
       </c>
       <c r="E76" s="3">
-        <v>8806200</v>
+        <v>8718300</v>
       </c>
       <c r="F76" s="3">
-        <v>8267800</v>
+        <v>8185200</v>
       </c>
       <c r="G76" s="3">
-        <v>7470000</v>
+        <v>7395400</v>
       </c>
       <c r="H76" s="3">
-        <v>6946400</v>
+        <v>6877000</v>
       </c>
       <c r="I76" s="3">
-        <v>6355900</v>
+        <v>6292400</v>
       </c>
       <c r="J76" s="3">
-        <v>6456900</v>
+        <v>6392400</v>
       </c>
       <c r="K76" s="3">
         <v>5703500</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-640000</v>
+        <v>-633600</v>
       </c>
       <c r="E81" s="3">
-        <v>961400</v>
+        <v>951800</v>
       </c>
       <c r="F81" s="3">
-        <v>1006800</v>
+        <v>996700</v>
       </c>
       <c r="G81" s="3">
-        <v>447600</v>
+        <v>443100</v>
       </c>
       <c r="H81" s="3">
-        <v>472200</v>
+        <v>467500</v>
       </c>
       <c r="I81" s="3">
-        <v>190700</v>
+        <v>188800</v>
       </c>
       <c r="J81" s="3">
-        <v>267200</v>
+        <v>264500</v>
       </c>
       <c r="K81" s="3">
         <v>168100</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>374700</v>
+        <v>371000</v>
       </c>
       <c r="E83" s="3">
-        <v>392700</v>
+        <v>388800</v>
       </c>
       <c r="F83" s="3">
-        <v>411100</v>
+        <v>407000</v>
       </c>
       <c r="G83" s="3">
-        <v>330700</v>
+        <v>327400</v>
       </c>
       <c r="H83" s="3">
-        <v>361200</v>
+        <v>357600</v>
       </c>
       <c r="I83" s="3">
-        <v>339900</v>
+        <v>336500</v>
       </c>
       <c r="J83" s="3">
-        <v>374600</v>
+        <v>370900</v>
       </c>
       <c r="K83" s="3">
         <v>376600</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1360100</v>
+        <v>1346500</v>
       </c>
       <c r="E89" s="3">
-        <v>1371500</v>
+        <v>1357800</v>
       </c>
       <c r="F89" s="3">
-        <v>1311000</v>
+        <v>1297900</v>
       </c>
       <c r="G89" s="3">
-        <v>1103100</v>
+        <v>1092100</v>
       </c>
       <c r="H89" s="3">
-        <v>847600</v>
+        <v>839100</v>
       </c>
       <c r="I89" s="3">
-        <v>651500</v>
+        <v>645000</v>
       </c>
       <c r="J89" s="3">
-        <v>670500</v>
+        <v>663800</v>
       </c>
       <c r="K89" s="3">
         <v>647900</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-715700</v>
+        <v>-708600</v>
       </c>
       <c r="E91" s="3">
-        <v>-194200</v>
+        <v>-192200</v>
       </c>
       <c r="F91" s="3">
-        <v>-1043600</v>
+        <v>-1033100</v>
       </c>
       <c r="G91" s="3">
-        <v>-428900</v>
+        <v>-424700</v>
       </c>
       <c r="H91" s="3">
-        <v>-610900</v>
+        <v>-604800</v>
       </c>
       <c r="I91" s="3">
-        <v>-1357900</v>
+        <v>-1344400</v>
       </c>
       <c r="J91" s="3">
-        <v>-687700</v>
+        <v>-680900</v>
       </c>
       <c r="K91" s="3">
         <v>-1027600</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-742500</v>
+        <v>-735100</v>
       </c>
       <c r="E94" s="3">
-        <v>-199700</v>
+        <v>-197700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1049700</v>
+        <v>-1039300</v>
       </c>
       <c r="G94" s="3">
-        <v>-424000</v>
+        <v>-419800</v>
       </c>
       <c r="H94" s="3">
-        <v>-598400</v>
+        <v>-592400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1356700</v>
+        <v>-1343100</v>
       </c>
       <c r="J94" s="3">
-        <v>-687300</v>
+        <v>-680500</v>
       </c>
       <c r="K94" s="3">
         <v>-948800</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-319700</v>
+        <v>-316500</v>
       </c>
       <c r="E96" s="3">
-        <v>-271100</v>
+        <v>-268400</v>
       </c>
       <c r="F96" s="3">
-        <v>-246400</v>
+        <v>-244000</v>
       </c>
       <c r="G96" s="3">
-        <v>-212600</v>
+        <v>-210400</v>
       </c>
       <c r="H96" s="3">
-        <v>-189600</v>
+        <v>-187700</v>
       </c>
       <c r="I96" s="3">
-        <v>-186800</v>
+        <v>-184900</v>
       </c>
       <c r="J96" s="3">
-        <v>-172600</v>
+        <v>-170900</v>
       </c>
       <c r="K96" s="3">
         <v>-162400</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-315700</v>
+        <v>-312600</v>
       </c>
       <c r="E100" s="3">
-        <v>-259300</v>
+        <v>-256800</v>
       </c>
       <c r="F100" s="3">
-        <v>-247300</v>
+        <v>-244800</v>
       </c>
       <c r="G100" s="3">
-        <v>-126000</v>
+        <v>-124700</v>
       </c>
       <c r="H100" s="3">
-        <v>-164400</v>
+        <v>-162700</v>
       </c>
       <c r="I100" s="3">
-        <v>106500</v>
+        <v>105400</v>
       </c>
       <c r="J100" s="3">
-        <v>328900</v>
+        <v>325600</v>
       </c>
       <c r="K100" s="3">
         <v>442500</v>
@@ -3708,13 +3708,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7400</v>
+        <v>7300</v>
       </c>
       <c r="E101" s="3">
-        <v>-10700</v>
+        <v>-10600</v>
       </c>
       <c r="F101" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="G101" s="3">
         <v>-1400</v>
@@ -3723,10 +3723,10 @@
         <v>800</v>
       </c>
       <c r="I101" s="3">
-        <v>-7000</v>
+        <v>-6900</v>
       </c>
       <c r="J101" s="3">
-        <v>42100</v>
+        <v>41700</v>
       </c>
       <c r="K101" s="3">
         <v>1200</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>309300</v>
+        <v>306200</v>
       </c>
       <c r="E102" s="3">
-        <v>901800</v>
+        <v>892800</v>
       </c>
       <c r="F102" s="3">
-        <v>7000</v>
+        <v>6900</v>
       </c>
       <c r="G102" s="3">
-        <v>551800</v>
+        <v>546300</v>
       </c>
       <c r="H102" s="3">
-        <v>85600</v>
+        <v>84800</v>
       </c>
       <c r="I102" s="3">
-        <v>-605700</v>
+        <v>-599600</v>
       </c>
       <c r="J102" s="3">
-        <v>354200</v>
+        <v>350600</v>
       </c>
       <c r="K102" s="3">
         <v>142800</v>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>FNV</t>
   </si>
@@ -717,25 +717,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1656000</v>
+        <v>1216900</v>
       </c>
       <c r="E8" s="3">
-        <v>1787400</v>
+        <v>1313600</v>
       </c>
       <c r="F8" s="3">
-        <v>1766100</v>
+        <v>1297600</v>
       </c>
       <c r="G8" s="3">
-        <v>1385900</v>
+        <v>1017300</v>
       </c>
       <c r="H8" s="3">
-        <v>1146700</v>
+        <v>841700</v>
       </c>
       <c r="I8" s="3">
-        <v>887400</v>
+        <v>650900</v>
       </c>
       <c r="J8" s="3">
-        <v>917000</v>
+        <v>672700</v>
       </c>
       <c r="K8" s="3">
         <v>839300</v>
@@ -753,25 +753,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>614600</v>
+        <v>177200</v>
       </c>
       <c r="E9" s="3">
-        <v>629100</v>
+        <v>174800</v>
       </c>
       <c r="F9" s="3">
-        <v>649200</v>
+        <v>175900</v>
       </c>
       <c r="G9" s="3">
-        <v>543100</v>
+        <v>155900</v>
       </c>
       <c r="H9" s="3">
-        <v>554300</v>
+        <v>142400</v>
       </c>
       <c r="I9" s="3">
-        <v>497100</v>
+        <v>115900</v>
       </c>
       <c r="J9" s="3">
-        <v>563800</v>
+        <v>139700</v>
       </c>
       <c r="K9" s="3">
         <v>522100</v>
@@ -789,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1041400</v>
+        <v>1039700</v>
       </c>
       <c r="E10" s="3">
-        <v>1158300</v>
+        <v>1138800</v>
       </c>
       <c r="F10" s="3">
-        <v>1116800</v>
+        <v>1121700</v>
       </c>
       <c r="G10" s="3">
-        <v>842800</v>
+        <v>861400</v>
       </c>
       <c r="H10" s="3">
-        <v>592400</v>
+        <v>699300</v>
       </c>
       <c r="I10" s="3">
-        <v>390300</v>
+        <v>535000</v>
       </c>
       <c r="J10" s="3">
-        <v>353200</v>
+        <v>533000</v>
       </c>
       <c r="K10" s="3">
         <v>317200</v>
@@ -858,8 +858,8 @@
       <c r="I12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
-        <v>4900</v>
+      <c r="J12" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K12" s="3">
         <v>4700</v>
@@ -913,25 +913,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1593900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-92400</v>
+        <v>-3700</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
-        <v>356100</v>
+        <v>1400</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>103200</v>
+        <v>-2000</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>6100</v>
+        <v>2700</v>
       </c>
       <c r="K14" s="3">
         <v>73500</v>
@@ -949,25 +949,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1446400</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>286200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>231600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>499100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>263200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>323700</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>273000</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
@@ -998,25 +998,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2237400</v>
+        <v>1648600</v>
       </c>
       <c r="E17" s="3">
-        <v>672500</v>
+        <v>492900</v>
       </c>
       <c r="F17" s="3">
-        <v>596800</v>
+        <v>436900</v>
       </c>
       <c r="G17" s="3">
-        <v>928800</v>
+        <v>676800</v>
       </c>
       <c r="H17" s="3">
-        <v>589500</v>
+        <v>431500</v>
       </c>
       <c r="I17" s="3">
-        <v>630900</v>
+        <v>462100</v>
       </c>
       <c r="J17" s="3">
-        <v>603300</v>
+        <v>437300</v>
       </c>
       <c r="K17" s="3">
         <v>625600</v>
@@ -1034,25 +1034,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-581400</v>
+        <v>-431700</v>
       </c>
       <c r="E18" s="3">
-        <v>1114900</v>
+        <v>820700</v>
       </c>
       <c r="F18" s="3">
-        <v>1169300</v>
+        <v>860700</v>
       </c>
       <c r="G18" s="3">
-        <v>457100</v>
+        <v>340500</v>
       </c>
       <c r="H18" s="3">
-        <v>557300</v>
+        <v>410200</v>
       </c>
       <c r="I18" s="3">
-        <v>256500</v>
+        <v>188800</v>
       </c>
       <c r="J18" s="3">
-        <v>313700</v>
+        <v>235400</v>
       </c>
       <c r="K18" s="3">
         <v>213800</v>
@@ -1086,25 +1086,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>87500</v>
+        <v>-12100</v>
       </c>
       <c r="E20" s="3">
-        <v>19000</v>
+        <v>-1400</v>
       </c>
       <c r="F20" s="3">
-        <v>-2000</v>
+        <v>5200</v>
       </c>
       <c r="G20" s="3">
-        <v>6000</v>
+        <v>1900</v>
       </c>
       <c r="H20" s="3">
-        <v>5700</v>
+        <v>1300</v>
       </c>
       <c r="I20" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="J20" s="3">
-        <v>6900</v>
+        <v>1200</v>
       </c>
       <c r="K20" s="3">
         <v>17200</v>
@@ -1122,25 +1122,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-123100</v>
+        <v>1026800</v>
       </c>
       <c r="E21" s="3">
-        <v>1522600</v>
+        <v>1108300</v>
       </c>
       <c r="F21" s="3">
-        <v>1574100</v>
+        <v>1087100</v>
       </c>
       <c r="G21" s="3">
-        <v>790400</v>
+        <v>837700</v>
       </c>
       <c r="H21" s="3">
-        <v>920400</v>
+        <v>672100</v>
       </c>
       <c r="I21" s="3">
-        <v>593300</v>
+        <v>512200</v>
       </c>
       <c r="J21" s="3">
-        <v>691300</v>
+        <v>507200</v>
       </c>
       <c r="K21" s="3">
         <v>605500</v>
@@ -1158,22 +1158,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="E22" s="3">
-        <v>1400</v>
+        <v>100</v>
       </c>
       <c r="F22" s="3">
-        <v>1900</v>
+        <v>300</v>
       </c>
       <c r="G22" s="3">
-        <v>1900</v>
+        <v>400</v>
       </c>
       <c r="H22" s="3">
-        <v>11500</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
+        <v>7600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1500</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>8</v>
@@ -1194,25 +1194,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-494800</v>
+        <v>-364200</v>
       </c>
       <c r="E23" s="3">
-        <v>1132600</v>
+        <v>833700</v>
       </c>
       <c r="F23" s="3">
-        <v>1165300</v>
+        <v>857800</v>
       </c>
       <c r="G23" s="3">
-        <v>461200</v>
+        <v>339500</v>
       </c>
       <c r="H23" s="3">
-        <v>551400</v>
+        <v>405900</v>
       </c>
       <c r="I23" s="3">
-        <v>256900</v>
+        <v>189100</v>
       </c>
       <c r="J23" s="3">
-        <v>320600</v>
+        <v>236000</v>
       </c>
       <c r="K23" s="3">
         <v>230900</v>
@@ -1230,25 +1230,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>138800</v>
+        <v>102200</v>
       </c>
       <c r="E24" s="3">
-        <v>180800</v>
+        <v>133100</v>
       </c>
       <c r="F24" s="3">
-        <v>168600</v>
+        <v>124100</v>
       </c>
       <c r="G24" s="3">
-        <v>18100</v>
+        <v>13300</v>
       </c>
       <c r="H24" s="3">
-        <v>84000</v>
+        <v>61800</v>
       </c>
       <c r="I24" s="3">
-        <v>65300</v>
+        <v>50100</v>
       </c>
       <c r="J24" s="3">
-        <v>46500</v>
+        <v>41300</v>
       </c>
       <c r="K24" s="3">
         <v>62900</v>
@@ -1302,25 +1302,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-633600</v>
+        <v>-466400</v>
       </c>
       <c r="E26" s="3">
-        <v>951800</v>
+        <v>700600</v>
       </c>
       <c r="F26" s="3">
-        <v>996700</v>
+        <v>733700</v>
       </c>
       <c r="G26" s="3">
-        <v>443100</v>
+        <v>326200</v>
       </c>
       <c r="H26" s="3">
-        <v>467500</v>
+        <v>344100</v>
       </c>
       <c r="I26" s="3">
-        <v>191500</v>
+        <v>139000</v>
       </c>
       <c r="J26" s="3">
-        <v>274100</v>
+        <v>194700</v>
       </c>
       <c r="K26" s="3">
         <v>168100</v>
@@ -1338,25 +1338,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-633600</v>
+        <v>-466400</v>
       </c>
       <c r="E27" s="3">
-        <v>951800</v>
+        <v>700600</v>
       </c>
       <c r="F27" s="3">
-        <v>996700</v>
+        <v>733700</v>
       </c>
       <c r="G27" s="3">
-        <v>443100</v>
+        <v>326200</v>
       </c>
       <c r="H27" s="3">
-        <v>467500</v>
+        <v>344100</v>
       </c>
       <c r="I27" s="3">
-        <v>191500</v>
+        <v>139000</v>
       </c>
       <c r="J27" s="3">
-        <v>274100</v>
+        <v>194700</v>
       </c>
       <c r="K27" s="3">
         <v>168100</v>
@@ -1409,26 +1409,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-2700</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-9600</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1518,25 +1518,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-87500</v>
+        <v>12100</v>
       </c>
       <c r="E32" s="3">
-        <v>-19000</v>
+        <v>1400</v>
       </c>
       <c r="F32" s="3">
-        <v>2000</v>
+        <v>-5200</v>
       </c>
       <c r="G32" s="3">
-        <v>-6000</v>
+        <v>-1900</v>
       </c>
       <c r="H32" s="3">
-        <v>-5700</v>
+        <v>-1300</v>
       </c>
       <c r="I32" s="3">
-        <v>-400</v>
+        <v>-300</v>
       </c>
       <c r="J32" s="3">
-        <v>-6900</v>
+        <v>-1200</v>
       </c>
       <c r="K32" s="3">
         <v>-17200</v>
@@ -1554,25 +1554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-633600</v>
+        <v>-466400</v>
       </c>
       <c r="E33" s="3">
-        <v>951800</v>
+        <v>700600</v>
       </c>
       <c r="F33" s="3">
-        <v>996700</v>
+        <v>733700</v>
       </c>
       <c r="G33" s="3">
-        <v>443100</v>
+        <v>326200</v>
       </c>
       <c r="H33" s="3">
-        <v>467500</v>
+        <v>344100</v>
       </c>
       <c r="I33" s="3">
-        <v>188800</v>
+        <v>139000</v>
       </c>
       <c r="J33" s="3">
-        <v>264500</v>
+        <v>194700</v>
       </c>
       <c r="K33" s="3">
         <v>168100</v>
@@ -1626,25 +1626,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-633600</v>
+        <v>-466400</v>
       </c>
       <c r="E35" s="3">
-        <v>951800</v>
+        <v>700600</v>
       </c>
       <c r="F35" s="3">
-        <v>996700</v>
+        <v>733700</v>
       </c>
       <c r="G35" s="3">
-        <v>443100</v>
+        <v>326200</v>
       </c>
       <c r="H35" s="3">
-        <v>467500</v>
+        <v>344100</v>
       </c>
       <c r="I35" s="3">
-        <v>188800</v>
+        <v>139000</v>
       </c>
       <c r="J35" s="3">
-        <v>264500</v>
+        <v>194700</v>
       </c>
       <c r="K35" s="3">
         <v>168100</v>
@@ -1735,25 +1735,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1931700</v>
+        <v>1421900</v>
       </c>
       <c r="E41" s="3">
-        <v>1625400</v>
+        <v>1196500</v>
       </c>
       <c r="F41" s="3">
-        <v>732600</v>
+        <v>539300</v>
       </c>
       <c r="G41" s="3">
-        <v>725700</v>
+        <v>534200</v>
       </c>
       <c r="H41" s="3">
-        <v>179500</v>
+        <v>132100</v>
       </c>
       <c r="I41" s="3">
-        <v>94700</v>
+        <v>69700</v>
       </c>
       <c r="J41" s="3">
-        <v>694300</v>
+        <v>511100</v>
       </c>
       <c r="K41" s="3">
         <v>348000</v>
@@ -1807,25 +1807,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>150800</v>
+        <v>111000</v>
       </c>
       <c r="E43" s="3">
-        <v>184300</v>
+        <v>135700</v>
       </c>
       <c r="F43" s="3">
-        <v>216700</v>
+        <v>159500</v>
       </c>
       <c r="G43" s="3">
-        <v>126900</v>
+        <v>93400</v>
       </c>
       <c r="H43" s="3">
-        <v>132900</v>
+        <v>97800</v>
       </c>
       <c r="I43" s="3">
-        <v>102600</v>
+        <v>75500</v>
       </c>
       <c r="J43" s="3">
-        <v>89500</v>
+        <v>65900</v>
       </c>
       <c r="K43" s="3">
         <v>97800</v>
@@ -1842,26 +1842,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
+      <c r="D44" s="3">
+        <v>500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>100</v>
+      </c>
+      <c r="F44" s="3">
+        <v>500</v>
+      </c>
+      <c r="G44" s="3">
+        <v>500</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
       <c r="J44" s="3">
-        <v>9600</v>
+        <v>7100</v>
       </c>
       <c r="K44" s="3">
         <v>3700</v>
@@ -1879,25 +1879,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>111900</v>
+        <v>51900</v>
       </c>
       <c r="E45" s="3">
-        <v>69100</v>
+        <v>28700</v>
       </c>
       <c r="F45" s="3">
-        <v>71500</v>
+        <v>33300</v>
       </c>
       <c r="G45" s="3">
-        <v>49000</v>
+        <v>19200</v>
       </c>
       <c r="H45" s="3">
-        <v>66300</v>
+        <v>26900</v>
       </c>
       <c r="I45" s="3">
-        <v>45200</v>
+        <v>27900</v>
       </c>
       <c r="J45" s="3">
-        <v>43900</v>
+        <v>15300</v>
       </c>
       <c r="K45" s="3">
         <v>47300</v>
@@ -1915,25 +1915,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2194400</v>
+        <v>1615300</v>
       </c>
       <c r="E46" s="3">
-        <v>1878900</v>
+        <v>1383100</v>
       </c>
       <c r="F46" s="3">
-        <v>1020800</v>
+        <v>751400</v>
       </c>
       <c r="G46" s="3">
-        <v>901600</v>
+        <v>663700</v>
       </c>
       <c r="H46" s="3">
-        <v>378600</v>
+        <v>278700</v>
       </c>
       <c r="I46" s="3">
-        <v>242500</v>
+        <v>178500</v>
       </c>
       <c r="J46" s="3">
-        <v>837400</v>
+        <v>616400</v>
       </c>
       <c r="K46" s="3">
         <v>496800</v>
@@ -1951,25 +1951,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>368400</v>
+        <v>254500</v>
       </c>
       <c r="E47" s="3">
-        <v>305100</v>
+        <v>227200</v>
       </c>
       <c r="F47" s="3">
-        <v>319400</v>
+        <v>235900</v>
       </c>
       <c r="G47" s="3">
-        <v>316100</v>
+        <v>201300</v>
       </c>
       <c r="H47" s="3">
-        <v>244800</v>
+        <v>148600</v>
       </c>
       <c r="I47" s="3">
-        <v>229600</v>
+        <v>137400</v>
       </c>
       <c r="J47" s="3">
-        <v>274800</v>
+        <v>203100</v>
       </c>
       <c r="K47" s="3">
         <v>201500</v>
@@ -1987,25 +1987,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>5479800</v>
+        <v>4033700</v>
       </c>
       <c r="E48" s="3">
-        <v>6703100</v>
+        <v>4934200</v>
       </c>
       <c r="F48" s="3">
-        <v>7005000</v>
+        <v>5156400</v>
       </c>
       <c r="G48" s="3">
-        <v>6302800</v>
+        <v>4639500</v>
       </c>
       <c r="H48" s="3">
-        <v>6534400</v>
+        <v>4810000</v>
       </c>
       <c r="I48" s="3">
-        <v>6203300</v>
+        <v>4566300</v>
       </c>
       <c r="J48" s="3">
-        <v>5369500</v>
+        <v>3952500</v>
       </c>
       <c r="K48" s="3">
         <v>5066000</v>
@@ -2131,25 +2131,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100400</v>
+        <v>27700</v>
       </c>
       <c r="E52" s="3">
-        <v>115300</v>
+        <v>40900</v>
       </c>
       <c r="F52" s="3">
-        <v>91000</v>
+        <v>15600</v>
       </c>
       <c r="G52" s="3">
-        <v>77400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>15900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>24500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>23400</v>
+        <v>4900</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>42500</v>
@@ -2203,25 +2203,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>8143000</v>
+        <v>5994100</v>
       </c>
       <c r="E54" s="3">
-        <v>9002500</v>
+        <v>6626800</v>
       </c>
       <c r="F54" s="3">
-        <v>8436100</v>
+        <v>6209900</v>
       </c>
       <c r="G54" s="3">
-        <v>7598000</v>
+        <v>5592900</v>
       </c>
       <c r="H54" s="3">
-        <v>7173700</v>
+        <v>5280600</v>
       </c>
       <c r="I54" s="3">
-        <v>6699900</v>
+        <v>4931800</v>
       </c>
       <c r="J54" s="3">
-        <v>6505000</v>
+        <v>4788400</v>
       </c>
       <c r="K54" s="3">
         <v>5806800</v>
@@ -2271,25 +2271,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7500</v>
+        <v>5500</v>
       </c>
       <c r="E57" s="3">
-        <v>9500</v>
+        <v>7000</v>
       </c>
       <c r="F57" s="3">
-        <v>11500</v>
+        <v>8500</v>
       </c>
       <c r="G57" s="3">
-        <v>4800</v>
+        <v>3500</v>
       </c>
       <c r="H57" s="3">
-        <v>9200</v>
+        <v>6800</v>
       </c>
       <c r="I57" s="3">
-        <v>9900</v>
+        <v>7300</v>
       </c>
       <c r="J57" s="3">
-        <v>8400</v>
+        <v>6200</v>
       </c>
       <c r="K57" s="3">
         <v>13200</v>
@@ -2343,25 +2343,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>45800</v>
+        <v>8300</v>
       </c>
       <c r="E59" s="3">
-        <v>58700</v>
+        <v>7100</v>
       </c>
       <c r="F59" s="3">
-        <v>47100</v>
+        <v>9600</v>
       </c>
       <c r="G59" s="3">
-        <v>67500</v>
+        <v>12400</v>
       </c>
       <c r="H59" s="3">
-        <v>63300</v>
+        <v>11600</v>
       </c>
       <c r="I59" s="3">
-        <v>24000</v>
+        <v>1400</v>
       </c>
       <c r="J59" s="3">
-        <v>22300</v>
+        <v>1100</v>
       </c>
       <c r="K59" s="3">
         <v>38500</v>
@@ -2379,25 +2379,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>53300</v>
+        <v>39200</v>
       </c>
       <c r="E60" s="3">
-        <v>68200</v>
+        <v>50200</v>
       </c>
       <c r="F60" s="3">
-        <v>58700</v>
+        <v>43200</v>
       </c>
       <c r="G60" s="3">
-        <v>72300</v>
+        <v>53200</v>
       </c>
       <c r="H60" s="3">
-        <v>72500</v>
+        <v>53400</v>
       </c>
       <c r="I60" s="3">
-        <v>34000</v>
+        <v>25000</v>
       </c>
       <c r="J60" s="3">
-        <v>30700</v>
+        <v>22600</v>
       </c>
       <c r="K60" s="3">
         <v>51700</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>112200</v>
+        <v>80000</v>
       </c>
       <c r="I61" s="3">
-        <v>282000</v>
+        <v>207600</v>
       </c>
       <c r="J61" s="3">
         <v>0</v>
@@ -2451,25 +2451,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>252400</v>
+        <v>5700</v>
       </c>
       <c r="E62" s="3">
-        <v>216000</v>
+        <v>6000</v>
       </c>
       <c r="F62" s="3">
-        <v>192200</v>
+        <v>6100</v>
       </c>
       <c r="G62" s="3">
-        <v>130300</v>
+        <v>4400</v>
       </c>
       <c r="H62" s="3">
-        <v>111900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>91400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>81900</v>
+        <v>2600</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>51600</v>
@@ -2595,25 +2595,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>305700</v>
+        <v>225000</v>
       </c>
       <c r="E66" s="3">
-        <v>284200</v>
+        <v>209200</v>
       </c>
       <c r="F66" s="3">
-        <v>250900</v>
+        <v>184700</v>
       </c>
       <c r="G66" s="3">
-        <v>202600</v>
+        <v>149100</v>
       </c>
       <c r="H66" s="3">
-        <v>296700</v>
+        <v>218400</v>
       </c>
       <c r="I66" s="3">
-        <v>407400</v>
+        <v>299900</v>
       </c>
       <c r="J66" s="3">
-        <v>112600</v>
+        <v>82900</v>
       </c>
       <c r="K66" s="3">
         <v>103300</v>
@@ -2791,25 +2791,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>288400</v>
+        <v>212300</v>
       </c>
       <c r="E72" s="3">
-        <v>1277500</v>
+        <v>940400</v>
       </c>
       <c r="F72" s="3">
-        <v>658700</v>
+        <v>484900</v>
       </c>
       <c r="G72" s="3">
-        <v>-46700</v>
+        <v>-34400</v>
       </c>
       <c r="H72" s="3">
-        <v>-223300</v>
+        <v>-164400</v>
       </c>
       <c r="I72" s="3">
-        <v>-437000</v>
+        <v>-321700</v>
       </c>
       <c r="J72" s="3">
-        <v>-421100</v>
+        <v>-310000</v>
       </c>
       <c r="K72" s="3">
         <v>-463300</v>
@@ -2935,25 +2935,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>7837300</v>
+        <v>5769100</v>
       </c>
       <c r="E76" s="3">
-        <v>8718300</v>
+        <v>6417600</v>
       </c>
       <c r="F76" s="3">
-        <v>8185200</v>
+        <v>6025200</v>
       </c>
       <c r="G76" s="3">
-        <v>7395400</v>
+        <v>5443800</v>
       </c>
       <c r="H76" s="3">
-        <v>6877000</v>
+        <v>5062200</v>
       </c>
       <c r="I76" s="3">
-        <v>6292400</v>
+        <v>4631900</v>
       </c>
       <c r="J76" s="3">
-        <v>6392400</v>
+        <v>4705500</v>
       </c>
       <c r="K76" s="3">
         <v>5703500</v>
@@ -3048,25 +3048,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-633600</v>
+        <v>-466400</v>
       </c>
       <c r="E81" s="3">
-        <v>951800</v>
+        <v>700600</v>
       </c>
       <c r="F81" s="3">
-        <v>996700</v>
+        <v>733700</v>
       </c>
       <c r="G81" s="3">
-        <v>443100</v>
+        <v>326200</v>
       </c>
       <c r="H81" s="3">
-        <v>467500</v>
+        <v>344100</v>
       </c>
       <c r="I81" s="3">
-        <v>188800</v>
+        <v>139000</v>
       </c>
       <c r="J81" s="3">
-        <v>264500</v>
+        <v>194700</v>
       </c>
       <c r="K81" s="3">
         <v>168100</v>
@@ -3100,25 +3100,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>371000</v>
+        <v>273100</v>
       </c>
       <c r="E83" s="3">
-        <v>388800</v>
+        <v>286200</v>
       </c>
       <c r="F83" s="3">
-        <v>407000</v>
+        <v>299600</v>
       </c>
       <c r="G83" s="3">
-        <v>327400</v>
+        <v>241000</v>
       </c>
       <c r="H83" s="3">
-        <v>357600</v>
+        <v>263200</v>
       </c>
       <c r="I83" s="3">
-        <v>336500</v>
+        <v>247700</v>
       </c>
       <c r="J83" s="3">
-        <v>370900</v>
+        <v>273000</v>
       </c>
       <c r="K83" s="3">
         <v>376600</v>
@@ -3316,25 +3316,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1346500</v>
+        <v>991200</v>
       </c>
       <c r="E89" s="3">
-        <v>1357800</v>
+        <v>999500</v>
       </c>
       <c r="F89" s="3">
-        <v>1297900</v>
+        <v>955400</v>
       </c>
       <c r="G89" s="3">
-        <v>1092100</v>
+        <v>803900</v>
       </c>
       <c r="H89" s="3">
-        <v>839100</v>
+        <v>617700</v>
       </c>
       <c r="I89" s="3">
-        <v>645000</v>
+        <v>474800</v>
       </c>
       <c r="J89" s="3">
-        <v>663800</v>
+        <v>488600</v>
       </c>
       <c r="K89" s="3">
         <v>647900</v>
@@ -3368,25 +3368,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-708600</v>
+        <v>-521600</v>
       </c>
       <c r="E91" s="3">
-        <v>-192200</v>
+        <v>-141500</v>
       </c>
       <c r="F91" s="3">
-        <v>-1033100</v>
+        <v>-760500</v>
       </c>
       <c r="G91" s="3">
-        <v>-424700</v>
+        <v>-312600</v>
       </c>
       <c r="H91" s="3">
-        <v>-604800</v>
+        <v>-445200</v>
       </c>
       <c r="I91" s="3">
-        <v>-1344400</v>
+        <v>-989600</v>
       </c>
       <c r="J91" s="3">
-        <v>-680900</v>
+        <v>-501200</v>
       </c>
       <c r="K91" s="3">
         <v>-1027600</v>
@@ -3476,25 +3476,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-735100</v>
+        <v>-541100</v>
       </c>
       <c r="E94" s="3">
-        <v>-197700</v>
+        <v>-145500</v>
       </c>
       <c r="F94" s="3">
-        <v>-1039300</v>
+        <v>-765000</v>
       </c>
       <c r="G94" s="3">
-        <v>-419800</v>
+        <v>-309000</v>
       </c>
       <c r="H94" s="3">
-        <v>-592400</v>
+        <v>-436100</v>
       </c>
       <c r="I94" s="3">
-        <v>-1343100</v>
+        <v>-988700</v>
       </c>
       <c r="J94" s="3">
-        <v>-680500</v>
+        <v>-500900</v>
       </c>
       <c r="K94" s="3">
         <v>-948800</v>
@@ -3528,25 +3528,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-316500</v>
+        <v>233000</v>
       </c>
       <c r="E96" s="3">
-        <v>-268400</v>
+        <v>197600</v>
       </c>
       <c r="F96" s="3">
-        <v>-244000</v>
+        <v>179600</v>
       </c>
       <c r="G96" s="3">
-        <v>-210400</v>
+        <v>154900</v>
       </c>
       <c r="H96" s="3">
-        <v>-187700</v>
+        <v>138200</v>
       </c>
       <c r="I96" s="3">
-        <v>-184900</v>
+        <v>136100</v>
       </c>
       <c r="J96" s="3">
-        <v>-170900</v>
+        <v>125800</v>
       </c>
       <c r="K96" s="3">
         <v>-162400</v>
@@ -3672,25 +3672,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-312600</v>
+        <v>-230100</v>
       </c>
       <c r="E100" s="3">
-        <v>-256800</v>
+        <v>-189000</v>
       </c>
       <c r="F100" s="3">
-        <v>-244800</v>
+        <v>-180200</v>
       </c>
       <c r="G100" s="3">
-        <v>-124700</v>
+        <v>-91800</v>
       </c>
       <c r="H100" s="3">
-        <v>-162700</v>
+        <v>-119800</v>
       </c>
       <c r="I100" s="3">
-        <v>105400</v>
+        <v>77600</v>
       </c>
       <c r="J100" s="3">
-        <v>325600</v>
+        <v>239700</v>
       </c>
       <c r="K100" s="3">
         <v>442500</v>
@@ -3708,25 +3708,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>7300</v>
+        <v>5400</v>
       </c>
       <c r="E101" s="3">
-        <v>-10600</v>
+        <v>-7800</v>
       </c>
       <c r="F101" s="3">
-        <v>-6900</v>
+        <v>-5100</v>
       </c>
       <c r="G101" s="3">
-        <v>-1400</v>
+        <v>-1000</v>
       </c>
       <c r="H101" s="3">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="I101" s="3">
-        <v>-6900</v>
+        <v>-5100</v>
       </c>
       <c r="J101" s="3">
-        <v>41700</v>
+        <v>30700</v>
       </c>
       <c r="K101" s="3">
         <v>1200</v>
@@ -3744,25 +3744,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>306200</v>
+        <v>225400</v>
       </c>
       <c r="E102" s="3">
-        <v>892800</v>
+        <v>657200</v>
       </c>
       <c r="F102" s="3">
-        <v>6900</v>
+        <v>5100</v>
       </c>
       <c r="G102" s="3">
-        <v>546300</v>
+        <v>402100</v>
       </c>
       <c r="H102" s="3">
-        <v>84800</v>
+        <v>62400</v>
       </c>
       <c r="I102" s="3">
-        <v>-599600</v>
+        <v>-441400</v>
       </c>
       <c r="J102" s="3">
-        <v>350600</v>
+        <v>258100</v>
       </c>
       <c r="K102" s="3">
         <v>142800</v>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
   <si>
     <t>FNV</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1102200</v>
+      </c>
+      <c r="E8" s="3">
         <v>1216900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1313600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1297600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1017300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>841700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>650900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>672700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>839300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>613400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>563500</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E9" s="3">
         <v>177200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>174800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>175900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>155900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>142400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>115900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>139700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>522100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>128700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>92900</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>975700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1039700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1138800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1121700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>861400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>699300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>535000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>533000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>317200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>484600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>470700</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +847,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,18 +874,21 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>4700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2800</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-3700</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3">
         <v>1400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2000</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>73500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>89700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>40100</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1446400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>286200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>231600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>499100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>263200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>323700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>273000</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>299100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>207800</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1648600</v>
+        <v>378500</v>
       </c>
       <c r="E17" s="3">
+        <v>1647600</v>
+      </c>
+      <c r="F17" s="3">
         <v>492900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>436900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>676800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>431500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>462100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>437300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>625600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>542200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>364400</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-431700</v>
+        <v>723700</v>
       </c>
       <c r="E18" s="3">
+        <v>-430700</v>
+      </c>
+      <c r="F18" s="3">
         <v>820700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>860700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>340500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>410200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>188800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>235400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>213800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>71200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>199100</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,80 +1112,87 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-12100</v>
+        <v>29100</v>
       </c>
       <c r="E20" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>5200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>17200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-4100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>900</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>919900</v>
+      </c>
+      <c r="E21" s="3">
         <v>1026800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1108300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1087100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>837700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>672100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>512200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>507200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>605500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>365600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>408500</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1164,19 +1203,19 @@
         <v>100</v>
       </c>
       <c r="F22" s="3">
+        <v>100</v>
+      </c>
+      <c r="G22" s="3">
         <v>300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -1187,81 +1226,90 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>763900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-364200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>833700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>857800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>339500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>405900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>189100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>236000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>230900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>67100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>211800</v>
+      </c>
+      <c r="E24" s="3">
         <v>102200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>133100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>124100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>50100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>62900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>33000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64100</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-466400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>700600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>733700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>326200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>344100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>139000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>194700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>168100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>135900</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-466400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>700600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>733700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>326200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>344100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>139000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>194700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>168100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>135900</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1430,8 +1490,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1439,9 +1499,12 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>12100</v>
+        <v>-29100</v>
       </c>
       <c r="E32" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F32" s="3">
         <v>1400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-5200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-17200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>4100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-900</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-466400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>700600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>733700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>326200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>344100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>139000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>194700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>168100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>135900</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-466400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>700600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>733700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>326200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>344100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>139000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>194700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>168100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>135900</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1814,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1451300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1421900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1196500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>539300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>534200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>132100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>511100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>348000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>206300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>754700</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1795,230 +1884,251 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>26000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>157700</v>
+      </c>
+      <c r="E43" s="3">
         <v>111000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>159500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>93400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>97800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>75500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>65900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>97800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>90000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>91800</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E44" s="3">
         <v>500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>500</v>
       </c>
       <c r="G44" s="3">
         <v>500</v>
       </c>
       <c r="H44" s="3">
+        <v>500</v>
+      </c>
+      <c r="I44" s="3">
         <v>4400</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3700</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>89900</v>
+      </c>
+      <c r="E45" s="3">
         <v>51900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>47300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>57500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>43700</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1716800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1615300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1383100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>751400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>663700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>278700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>178500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>616400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>496800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>379800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>890300</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>325500</v>
+      </c>
+      <c r="E47" s="3">
         <v>254500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>227200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>235900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>201300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>148600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>137400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>203100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>201500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>130900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>84700</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4109300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4033700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4934200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5156400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4639500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4810000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4566300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3952500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5066000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4527800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3358900</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2052,9 +2162,12 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,26 +2240,29 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E52" s="3">
         <v>27700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4900</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>8</v>
@@ -2151,18 +2270,21 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>42500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>82300</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6330400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5994100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6626800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6209900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5592900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5280600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>4931800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4788400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5806800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5080500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4416100</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,44 +2394,48 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E57" s="3">
         <v>5500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>6800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7900</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2336,81 +2469,90 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E59" s="3">
         <v>8300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>9600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>19000</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>67500</v>
+      </c>
+      <c r="E60" s="3">
         <v>39200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>50200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>53200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>25000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>22600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>51700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26900</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2427,62 +2569,68 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>80000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>207600</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3">
         <v>632300</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E62" s="3">
         <v>5700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2600</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>51600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51300</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>333800</v>
+      </c>
+      <c r="E66" s="3">
         <v>225000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>209200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>184700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>149100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>218400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>299900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>82900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>103300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>707000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>78200</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,9 +2876,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2748,9 +2915,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>486500</v>
+      </c>
+      <c r="E72" s="3">
         <v>212300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>940400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>484900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-34400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-164400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-321700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-310000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-463300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-417900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-252000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5996600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5769100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6417600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6025200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5443800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5062200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4631900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4705500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5703500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4373500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4337900</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>552100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-466400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>700600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>733700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>326200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>344100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>139000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>194700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>168100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>135900</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>225300</v>
+      </c>
+      <c r="E83" s="3">
         <v>273100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>286200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>299600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>241000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>263200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>247700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>273000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>376600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>299100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>207800</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>829500</v>
+      </c>
+      <c r="E89" s="3">
         <v>991200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>999500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>955400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>803900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>617700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>474800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>488600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>647900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>434600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>340100</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-521600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-141500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-760500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-312600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-445200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-989600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-501200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1027600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1410900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1135800</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-537300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-541100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-145500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-765000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-309000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-436100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-988700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-948800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1529400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1039300</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>242400</v>
+      </c>
+      <c r="E96" s="3">
         <v>233000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>197600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>179600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>154900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>138200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>136100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>125800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-162400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-130100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-115500</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-230100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-189000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-180200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-91800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-119800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>77600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>239700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>442500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>517300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>502800</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="E101" s="3">
         <v>5400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>30700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-35400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-29700</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E102" s="3">
         <v>225400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>657200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>402100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>62400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-441400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>258100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>142800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-613000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-226100</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -932,10 +932,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-300</v>
+        <v>6000</v>
       </c>
       <c r="E14" s="3">
-        <v>-3700</v>
+        <v>-2700</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1119,10 +1119,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>29100</v>
+        <v>22800</v>
       </c>
       <c r="E20" s="3">
-        <v>-11100</v>
+        <v>-12100</v>
       </c>
       <c r="F20" s="3">
         <v>-1400</v>
@@ -1158,10 +1158,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>919900</v>
+        <v>926200</v>
       </c>
       <c r="E21" s="3">
-        <v>1026800</v>
+        <v>1027800</v>
       </c>
       <c r="F21" s="3">
         <v>1108300</v>
@@ -1587,10 +1587,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-29100</v>
+        <v>-22800</v>
       </c>
       <c r="E32" s="3">
-        <v>11100</v>
+        <v>12100</v>
       </c>
       <c r="F32" s="3">
         <v>1400</v>

--- a/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FNV_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>FNV</t>
   </si>
@@ -656,183 +656,195 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2"/>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1804100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1102200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1216900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1313600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1297600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1017300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>841700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>650900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>672700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>839300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>613400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>563500</v>
       </c>
-      <c r="O8" s="3"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>164300</v>
+      </c>
+      <c r="E9" s="3">
         <v>126500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>177200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>174800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>175900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>155900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>142400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>115900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>139700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>522100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>128700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>92900</v>
       </c>
-      <c r="O9" s="3"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1639800</v>
+      </c>
+      <c r="E10" s="3">
         <v>975700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1039700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1138800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1121700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>861400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>699300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>535000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>533000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>317200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>484600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>470700</v>
       </c>
-      <c r="O10" s="3"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +860,9 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -877,18 +890,21 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3">
         <v>4700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2800</v>
       </c>
-      <c r="O12" s="3"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,87 +941,96 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-      <c r="O13" s="3"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2700</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2000</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>73500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>89700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>40100</v>
       </c>
-      <c r="O14" s="3"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>301900</v>
+      </c>
+      <c r="E15" s="3">
         <v>225300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1446400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>286200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>231600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>499100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>263200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>323700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>273000</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>299100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>207800</v>
       </c>
-      <c r="O15" s="3"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1018,86 +1043,93 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>458300</v>
+      </c>
+      <c r="E17" s="3">
         <v>378500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1647600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>492900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>436900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>676800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>431500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>462100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>437300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>625600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>542200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>364400</v>
       </c>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3"/>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1345800</v>
+      </c>
+      <c r="E18" s="3">
         <v>723700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-430700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>820700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>860700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>340500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>410200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>188800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>235400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>213800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>71200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>199100</v>
       </c>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3"/>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1113,91 +1145,98 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E20" s="3">
         <v>22800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>5200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>900</v>
       </c>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3"/>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1682000</v>
+      </c>
+      <c r="E21" s="3">
         <v>926200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1027800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1108300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1087100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>837700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>672100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>512200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>507200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>605500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>365600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>408500</v>
       </c>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3"/>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>100</v>
@@ -1206,19 +1245,19 @@
         <v>100</v>
       </c>
       <c r="G22" s="3">
+        <v>100</v>
+      </c>
+      <c r="H22" s="3">
         <v>300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>8</v>
@@ -1229,87 +1268,96 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3"/>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1416000</v>
+      </c>
+      <c r="E23" s="3">
         <v>763900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-364200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>833700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>857800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>339500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>405900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>189100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>236000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>230900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>67100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>200000</v>
       </c>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3"/>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>303900</v>
+      </c>
+      <c r="E24" s="3">
         <v>211800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>102200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>133100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>124100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>61800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>50100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>33000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64100</v>
       </c>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3"/>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1346,87 +1394,96 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3"/>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E26" s="3">
         <v>552100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-466400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>700600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>733700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>326200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>344100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>139000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>194700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>168100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>34000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>135900</v>
       </c>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3"/>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E27" s="3">
         <v>552100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-466400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>700600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>733700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>326200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>344100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>139000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>194700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>168100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>34000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>135900</v>
       </c>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3"/>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1463,9 +1520,12 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-      <c r="O28" s="3"/>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3"/>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1493,8 +1553,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1502,9 +1562,12 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3"/>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P29" s="3"/>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1541,9 +1604,12 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-      <c r="O30" s="3"/>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3"/>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1580,87 +1646,96 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-      <c r="O31" s="3"/>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3"/>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-22800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-5200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-900</v>
       </c>
-      <c r="O32" s="3"/>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3"/>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E33" s="3">
         <v>552100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-466400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>700600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>733700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>326200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>344100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>139000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>194700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>168100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>34000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>135900</v>
       </c>
-      <c r="O33" s="3"/>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3"/>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1697,92 +1772,101 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3"/>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E35" s="3">
         <v>552100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-466400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>700600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>733700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>326200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>344100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>139000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>194700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>168100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>34000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>135900</v>
       </c>
-      <c r="O35" s="3"/>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3"/>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1798,8 +1882,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1815,47 +1900,51 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>670900</v>
+      </c>
+      <c r="E41" s="3">
         <v>1451300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1421900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1196500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>539300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>534200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>511100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>348000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>206300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>754700</v>
       </c>
-      <c r="O41" s="3"/>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1887,248 +1976,269 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>26000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3"/>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3"/>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>157700</v>
+        <v>257100</v>
       </c>
       <c r="E43" s="3">
+        <v>165800</v>
+      </c>
+      <c r="F43" s="3">
         <v>111000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>159500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>93400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>97800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>75500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>65900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>97800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>90000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>91800</v>
       </c>
-      <c r="O43" s="3"/>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>600</v>
+      </c>
+      <c r="E44" s="3">
         <v>7300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>500</v>
       </c>
       <c r="H44" s="3">
         <v>500</v>
       </c>
       <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>4400</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3700</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3"/>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E45" s="3">
         <v>89900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>51900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>47300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>57500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>43700</v>
       </c>
-      <c r="O45" s="3"/>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3"/>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1021400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1716800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1615300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1383100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>751400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>663700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>278700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>178500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>616400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>496800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>379800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>890300</v>
       </c>
-      <c r="O46" s="3"/>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1141300</v>
+      </c>
+      <c r="E47" s="3">
         <v>325500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>254500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>227200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>235900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>201300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>148600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>137400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>203100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>201500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>130900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>84700</v>
       </c>
-      <c r="O47" s="3"/>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6054400</v>
+      </c>
+      <c r="E48" s="3">
         <v>4109300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4033700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4934200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5156400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4639500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4810000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4566300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3952500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5066000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4527800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3358900</v>
       </c>
-      <c r="O48" s="3"/>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3"/>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2165,9 +2275,12 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3"/>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3"/>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2204,9 +2317,12 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-      <c r="O50" s="3"/>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3"/>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2243,29 +2359,32 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-      <c r="O51" s="3"/>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3"/>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>42500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>27700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4900</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>8</v>
@@ -2273,18 +2392,21 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>42500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>82300</v>
       </c>
-      <c r="O52" s="3"/>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3"/>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2321,48 +2443,54 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-      <c r="O53" s="3"/>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3"/>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8241400</v>
+      </c>
+      <c r="E54" s="3">
         <v>6330400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5994100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6626800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6209900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5592900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5280600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>4931800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4788400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5806800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5080500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4416100</v>
       </c>
-      <c r="O54" s="3"/>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2378,8 +2506,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2395,47 +2524,51 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7900</v>
       </c>
-      <c r="O57" s="3"/>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3"/>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2472,87 +2605,96 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3"/>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3"/>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E59" s="3">
         <v>38800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>19000</v>
       </c>
-      <c r="O59" s="3"/>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3"/>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E60" s="3">
         <v>67500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>50200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>53200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>53400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>22600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>51700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>28800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26900</v>
       </c>
-      <c r="O60" s="3"/>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3"/>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2572,65 +2714,71 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
+        <v>0</v>
+      </c>
+      <c r="J61" s="3">
         <v>80000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>207600</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
       <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3">
         <v>632300</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3"/>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3"/>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E62" s="3">
         <v>28300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>5700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>6000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2600</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>51600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51300</v>
       </c>
-      <c r="O62" s="3"/>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3"/>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2667,9 +2815,12 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-      <c r="O63" s="3"/>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3"/>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2706,9 +2857,12 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-      <c r="O64" s="3"/>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3"/>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2745,48 +2899,54 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-      <c r="O65" s="3"/>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3"/>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>606100</v>
+      </c>
+      <c r="E66" s="3">
         <v>333800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>225000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>209200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>184700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>149100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>218400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>299900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>82900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>707000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>78200</v>
       </c>
-      <c r="O66" s="3"/>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3"/>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2802,8 +2962,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2840,9 +3001,12 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-      <c r="O68" s="3"/>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3"/>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2879,9 +3043,12 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-      <c r="O69" s="3"/>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3"/>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2918,9 +3085,12 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-      <c r="O70" s="3"/>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3"/>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2957,48 +3127,54 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-      <c r="O71" s="3"/>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3"/>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1379800</v>
+      </c>
+      <c r="E72" s="3">
         <v>486500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>212300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>940400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>484900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-34400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-164400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-321700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-310000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-463300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-417900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-252000</v>
       </c>
-      <c r="O72" s="3"/>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3"/>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3035,9 +3211,12 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-      <c r="O73" s="3"/>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3"/>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3074,9 +3253,12 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-      <c r="O74" s="3"/>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3"/>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3113,48 +3295,54 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-      <c r="O75" s="3"/>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3"/>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7635300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5996600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5769100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6417600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6025200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5443800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5062200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4631900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4705500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5703500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4373500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4337900</v>
       </c>
-      <c r="O76" s="3"/>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3"/>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3191,92 +3379,101 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-      <c r="O77" s="3"/>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3"/>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2"/>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1112100</v>
+      </c>
+      <c r="E81" s="3">
         <v>552100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-466400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>700600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>733700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>326200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>344100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>139000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>194700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>168100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>34000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>135900</v>
       </c>
-      <c r="O81" s="3"/>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3"/>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3292,47 +3489,51 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>306700</v>
+      </c>
+      <c r="E83" s="3">
         <v>225300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>273100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>286200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>299600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>241000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>263200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>247700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>273000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>376600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>299100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>207800</v>
       </c>
-      <c r="O83" s="3"/>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3"/>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3369,9 +3570,12 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-      <c r="O84" s="3"/>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3"/>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3408,9 +3612,12 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-      <c r="O85" s="3"/>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3"/>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3447,9 +3654,12 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-      <c r="O86" s="3"/>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3"/>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3486,9 +3696,12 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-      <c r="O87" s="3"/>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3"/>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3525,48 +3738,54 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-      <c r="O88" s="3"/>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3"/>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1493700</v>
+      </c>
+      <c r="E89" s="3">
         <v>829500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>991200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>999500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>955400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>803900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>617700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>474800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>488600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>647900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>434600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>340100</v>
       </c>
-      <c r="O89" s="3"/>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3"/>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3582,47 +3801,51 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2196700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-408000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-521600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-141500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-760500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-312600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-445200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-989600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-501200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1027600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1410900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1135800</v>
       </c>
-      <c r="O91" s="3"/>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3"/>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3659,9 +3882,12 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-      <c r="O92" s="3"/>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3"/>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3698,48 +3924,54 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-      <c r="O93" s="3"/>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3"/>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2033000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-537300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-541100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-145500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-765000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-309000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-436100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-988700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-948800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1529400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1039300</v>
       </c>
-      <c r="O94" s="3"/>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3"/>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3755,47 +3987,51 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>275100</v>
+      </c>
+      <c r="E96" s="3">
         <v>242400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>233000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>197600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>179600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>154900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>138200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>136100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>125800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-162400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-130100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-115500</v>
       </c>
-      <c r="O96" s="3"/>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3"/>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3832,9 +4068,12 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-      <c r="O97" s="3"/>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3"/>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3871,9 +4110,12 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-      <c r="O98" s="3"/>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3"/>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3910,124 +4152,136 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-      <c r="O99" s="3"/>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3"/>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-267400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-240400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-230100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-189000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-180200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-91800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-119800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>239700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>442500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>517300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>502800</v>
       </c>
-      <c r="O100" s="3"/>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3"/>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-22400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>30700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-35400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-29700</v>
       </c>
-      <c r="O101" s="3"/>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3"/>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-780400</v>
+      </c>
+      <c r="E102" s="3">
         <v>29400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>225400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>657200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>402100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>62400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-441400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>258100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>142800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-613000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-226100</v>
       </c>
-      <c r="O102" s="3"/>
+      <c r="P102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
